--- a/database/event/3061/event_3061_evp_summary.xlsx
+++ b/database/event/3061/event_3061_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.5994</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5594</v>
+        <v>3.4818</v>
       </c>
       <c r="E2" t="n">
         <v>9.8538</v>
@@ -548,7 +548,7 @@
         <v>2.0588</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7316</v>
+        <v>2.6655</v>
       </c>
       <c r="E3" t="n">
         <v>7.8047</v>
@@ -594,7 +594,7 @@
         <v>1.2717</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5261</v>
+        <v>1.4767</v>
       </c>
       <c r="E4" t="n">
         <v>4.8207</v>
@@ -640,7 +640,7 @@
         <v>1.084</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2387</v>
+        <v>1.1933</v>
       </c>
       <c r="E5" t="n">
         <v>4.1094</v>
@@ -686,7 +686,7 @@
         <v>0.945</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0258</v>
+        <v>0.9833</v>
       </c>
       <c r="E6" t="n">
         <v>3.5823</v>
@@ -732,7 +732,7 @@
         <v>0.8022</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8071</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>3.0409</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8331</v>
+        <v>3.0403</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7474</v>
+        <v>0.802</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7231</v>
+        <v>0.7673</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8331</v>
+        <v>3.0403</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8568</v>
+        <v>2.064</v>
       </c>
       <c r="G8" t="n">
         <v>0.9762999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8568</v>
+        <v>2.064</v>
       </c>
       <c r="I8" t="n">
-        <v>1.505</v>
+        <v>1.673</v>
       </c>
       <c r="J8" t="n">
         <v>0.9762999999999999</v>
@@ -805,7 +805,7 @@
         <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4813</v>
+        <v>2.6493</v>
       </c>
       <c r="N8" t="n">
         <v>200</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5336</v>
+        <v>2.8508</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6683</v>
+        <v>0.752</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6022</v>
+        <v>0.6918</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5336</v>
+        <v>2.8508</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0939</v>
+        <v>2.4111</v>
       </c>
       <c r="G9" t="n">
         <v>0.4397</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0939</v>
+        <v>2.4111</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6972</v>
+        <v>1.9542</v>
       </c>
       <c r="J9" t="n">
         <v>0.4397</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1369</v>
+        <v>2.3939</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5019</v>
+        <v>2.6009</v>
       </c>
       <c r="C10" t="n">
-        <v>0.66</v>
+        <v>0.6861</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5893</v>
+        <v>0.5923</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5019</v>
+        <v>2.6009</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5019</v>
+        <v>2.6009</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5019</v>
+        <v>2.6009</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5019</v>
+        <v>2.6009</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5019</v>
+        <v>2.6009</v>
       </c>
       <c r="N10" t="n">
         <v>148</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4837</v>
+        <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6552</v>
+        <v>0.6595</v>
       </c>
       <c r="D11" t="n">
-        <v>0.582</v>
+        <v>0.5521</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4837</v>
+        <v>2.5</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3316</v>
+        <v>2.3479</v>
       </c>
       <c r="G11" t="n">
         <v>0.1521</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3316</v>
+        <v>2.3479</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8898</v>
+        <v>1.903</v>
       </c>
       <c r="J11" t="n">
         <v>0.1521</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0419</v>
+        <v>2.0551</v>
       </c>
       <c r="N11" t="n">
         <v>186</v>
@@ -962,7 +962,7 @@
         <v>0.6126</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5167</v>
+        <v>0.4812</v>
       </c>
       <c r="E12" t="n">
         <v>2.3221</v>
@@ -1008,7 +1008,7 @@
         <v>0.5797</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4664</v>
+        <v>0.4316</v>
       </c>
       <c r="E13" t="n">
         <v>2.1976</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9288</v>
+        <v>2.1007</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5088</v>
+        <v>0.5542</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3578</v>
+        <v>0.393</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9288</v>
+        <v>2.1007</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0013</v>
+        <v>2.1732</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0725</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0013</v>
+        <v>2.1732</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6221</v>
+        <v>1.7614</v>
       </c>
       <c r="J14" t="n">
         <v>-0.0725</v>
@@ -1081,7 +1081,7 @@
         <v>173</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5496</v>
+        <v>1.6889</v>
       </c>
       <c r="N14" t="n">
         <v>278</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5832</v>
+        <v>1.936</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4176</v>
+        <v>0.5107</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2182</v>
+        <v>0.3274</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5832</v>
+        <v>1.936</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7117</v>
+        <v>2.4541</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8715000000000001</v>
+        <v>-0.5181</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7117</v>
+        <v>2.4541</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5768</v>
+        <v>1.9892</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8715000000000001</v>
+        <v>-0.5181</v>
       </c>
       <c r="K15" t="n">
         <v>132</v>
@@ -1127,7 +1127,7 @@
         <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4483</v>
+        <v>1.4711</v>
       </c>
       <c r="N15" t="n">
         <v>186</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5064</v>
+        <v>1.5832</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3974</v>
+        <v>0.4176</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1872</v>
+        <v>0.1868</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5064</v>
+        <v>1.5832</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0245</v>
+        <v>0.7117</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5181</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0245</v>
+        <v>0.7117</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6409</v>
+        <v>0.5768</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5181</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1228</v>
+        <v>1.4483</v>
       </c>
       <c r="N16" t="n">
         <v>186</v>
@@ -1192,7 +1192,7 @@
         <v>0.3811</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1622</v>
+        <v>0.1316</v>
       </c>
       <c r="E17" t="n">
         <v>1.4446</v>
@@ -1228,507 +1228,507 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0547</v>
+        <v>1.4296</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2782</v>
+        <v>0.3771</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0047</v>
+        <v>0.1256</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0547</v>
+        <v>1.4296</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4061</v>
+        <v>1.4296</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3514</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4061</v>
+        <v>1.4296</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1397</v>
+        <v>1.4296</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3514</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L18" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7883</v>
+        <v>1.4296</v>
       </c>
       <c r="N18" t="n">
-        <v>200</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.868</v>
+        <v>1.2379</v>
       </c>
       <c r="C19" t="n">
-        <v>0.229</v>
+        <v>0.3266</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0707</v>
+        <v>0.0493</v>
       </c>
       <c r="E19" t="n">
-        <v>0.868</v>
+        <v>1.2379</v>
       </c>
       <c r="F19" t="n">
-        <v>0.868</v>
+        <v>1.5893</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.3514</v>
       </c>
       <c r="H19" t="n">
-        <v>0.868</v>
+        <v>1.5893</v>
       </c>
       <c r="I19" t="n">
-        <v>0.868</v>
+        <v>1.2882</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3514</v>
       </c>
       <c r="K19" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M19" t="n">
-        <v>0.868</v>
+        <v>0.9368000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8158</v>
+        <v>1.0845</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2152</v>
+        <v>0.2861</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0118</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8158</v>
+        <v>1.0845</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8158</v>
+        <v>1.0845</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8158</v>
+        <v>1.0845</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8158</v>
+        <v>1.0845</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8158</v>
+        <v>1.0845</v>
       </c>
       <c r="N20" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.0004</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1972</v>
+        <v>0.2639</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1194</v>
+        <v>-0.0454</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.0004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.3671</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3667</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.3671</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.108</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3667</v>
       </c>
       <c r="K21" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7413000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.9571</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1804</v>
+        <v>0.2525</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.145</v>
+        <v>-0.0626</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.9571</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0507</v>
+        <v>0.9571</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3667</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0507</v>
+        <v>0.9571</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8516</v>
+        <v>0.9571</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3667</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4849</v>
+        <v>0.9571</v>
       </c>
       <c r="N22" t="n">
-        <v>200</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3544</v>
+        <v>0.8158</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0935</v>
+        <v>0.2152</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2782</v>
+        <v>-0.1189</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3544</v>
+        <v>0.8158</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0165</v>
+        <v>0.8158</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0165</v>
+        <v>0.8158</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8239</v>
+        <v>0.8158</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L23" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1617999999999999</v>
+        <v>0.8158</v>
       </c>
       <c r="N23" t="n">
-        <v>200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3205</v>
+        <v>0.5302</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1399</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2919</v>
+        <v>-0.2327</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3205</v>
+        <v>0.5302</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3205</v>
+        <v>1.1923</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3205</v>
+        <v>1.1923</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3205</v>
+        <v>0.9664</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="K24" t="n">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3205</v>
+        <v>0.3043</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2924</v>
+        <v>0.3205</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0771</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3032</v>
+        <v>-0.3162</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2924</v>
+        <v>0.3205</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2924</v>
+        <v>0.3205</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2924</v>
+        <v>0.3205</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2924</v>
+        <v>0.3205</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2924</v>
+        <v>0.3205</v>
       </c>
       <c r="N25" t="n">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1037</v>
+        <v>0.1654</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0274</v>
+        <v>0.0436</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3795</v>
+        <v>-0.378</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1037</v>
+        <v>0.1654</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1037</v>
+        <v>1.1343</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.9689</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1037</v>
+        <v>1.1343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1037</v>
+        <v>0.9194</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.9689</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1037</v>
+        <v>-0.04949999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>91</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0697</v>
+        <v>0.1037</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0184</v>
+        <v>0.0274</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3932</v>
+        <v>-0.4026</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0697</v>
+        <v>0.1037</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0697</v>
+        <v>0.1037</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0697</v>
+        <v>0.1037</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0697</v>
+        <v>0.1037</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0697</v>
+        <v>0.1037</v>
       </c>
       <c r="N27" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0178</v>
+        <v>0.0697</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0047</v>
+        <v>0.0184</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4142</v>
+        <v>-0.4161</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0178</v>
+        <v>0.0697</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9867</v>
+        <v>0.0697</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9689</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9867</v>
+        <v>0.0697</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7997</v>
+        <v>0.0697</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9689</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L28" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1692</v>
+        <v>0.0697</v>
       </c>
       <c r="N28" t="n">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
@@ -1744,7 +1744,7 @@
         <v>-0.0566</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.508</v>
+        <v>-0.5293</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2144</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0935</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5646</v>
+        <v>-0.5851</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3545</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1286</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6183</v>
+        <v>-0.6381</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4875</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1327</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6246</v>
+        <v>-0.6443</v>
       </c>
       <c r="E32" t="n">
         <v>-0.5031</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2407</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7899</v>
+        <v>-0.8074</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9123</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2654</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8278</v>
+        <v>-0.8447</v>
       </c>
       <c r="E34" t="n">
         <v>-1.006</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3002</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.881</v>
+        <v>-0.8972</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1379</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3076</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8924</v>
+        <v>-0.9084</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1659</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3675</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9841</v>
+        <v>-0.9989</v>
       </c>
       <c r="E37" t="n">
         <v>-1.393</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3708</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9892</v>
+        <v>-1.0039</v>
       </c>
       <c r="E38" t="n">
         <v>-1.4055</v>
@@ -2204,7 +2204,7 @@
         <v>-0.436</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0891</v>
+        <v>-1.1024</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6528</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4662</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1353</v>
+        <v>-1.148</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7672</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8583</v>
+        <v>-2.7612</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.754</v>
+        <v>-0.7284</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5761</v>
+        <v>-1.544</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8583</v>
+        <v>-2.7612</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8583</v>
+        <v>-0.7612</v>
       </c>
       <c r="G41" t="n">
         <v>-2</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8583</v>
+        <v>-0.7612</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6957</v>
+        <v>-0.617</v>
       </c>
       <c r="J41" t="n">
         <v>-2</v>
@@ -2323,7 +2323,7 @@
         <v>173</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6957</v>
+        <v>-2.617</v>
       </c>
       <c r="N41" t="n">
         <v>278</v>

--- a/database/event/3061/event_3061_evp_summary.xlsx
+++ b/database/event/3061/event_3061_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.8538</v>
+        <v>8.8194</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5994</v>
+        <v>2.3265</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4818</v>
+        <v>3.3435</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8538</v>
+        <v>8.8194</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2927</v>
+        <v>3.8957</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5612</v>
+        <v>4.9236</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7099</v>
+        <v>8.239800000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8175</v>
+        <v>4.2843</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5612</v>
+        <v>4.9236</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>201</v>
       </c>
       <c r="M2" t="n">
-        <v>9.3787</v>
+        <v>9.2079</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8047</v>
+        <v>6.9828</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0588</v>
+        <v>1.842</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6655</v>
+        <v>2.5144</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8047</v>
+        <v>6.9828</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6568</v>
+        <v>3.222</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1479</v>
+        <v>3.7608</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6568</v>
+        <v>5.8659</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9639</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1479</v>
+        <v>3.7608</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -575,7 +575,7 @@
         <v>201</v>
       </c>
       <c r="M3" t="n">
-        <v>7.111800000000001</v>
+        <v>6.8108</v>
       </c>
       <c r="N3" t="n">
         <v>342</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8207</v>
+        <v>5.2913</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2717</v>
+        <v>1.3958</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4767</v>
+        <v>1.7507</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8207</v>
+        <v>5.2913</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6539</v>
+        <v>2.8899</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1668</v>
+        <v>2.4014</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6539</v>
+        <v>4.696</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1511</v>
+        <v>2.4417</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1668</v>
+        <v>2.4014</v>
       </c>
       <c r="K4" t="n">
         <v>141</v>
@@ -621,7 +621,7 @@
         <v>201</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3179</v>
+        <v>4.8431</v>
       </c>
       <c r="N4" t="n">
         <v>342</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1094</v>
+        <v>4.2975</v>
       </c>
       <c r="C5" t="n">
-        <v>1.084</v>
+        <v>1.1337</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1933</v>
+        <v>1.3021</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1094</v>
+        <v>4.2975</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8786</v>
+        <v>2.3907</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2308</v>
+        <v>1.9068</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8786</v>
+        <v>2.9372</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5226</v>
+        <v>1.5272</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2308</v>
+        <v>1.9068</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -667,7 +667,7 @@
         <v>173</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7534</v>
+        <v>3.434</v>
       </c>
       <c r="N5" t="n">
         <v>278</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5823</v>
+        <v>3.7819</v>
       </c>
       <c r="C6" t="n">
-        <v>0.945</v>
+        <v>0.9976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9833</v>
+        <v>1.0693</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5823</v>
+        <v>3.7819</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8142</v>
+        <v>3.0183</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7681</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8142</v>
+        <v>5.1481</v>
       </c>
       <c r="I6" t="n">
-        <v>2.281</v>
+        <v>2.6768</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7681</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -713,7 +713,7 @@
         <v>173</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0491</v>
+        <v>3.4404</v>
       </c>
       <c r="N6" t="n">
         <v>278</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0409</v>
+        <v>3.7247</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8022</v>
+        <v>0.9826</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7675999999999999</v>
+        <v>1.0435</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0409</v>
+        <v>3.7247</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0326</v>
+        <v>3.0077</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0083</v>
+        <v>0.717</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0326</v>
+        <v>5.1108</v>
       </c>
       <c r="I7" t="n">
-        <v>2.458</v>
+        <v>2.6574</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0083</v>
+        <v>0.717</v>
       </c>
       <c r="K7" t="n">
         <v>141</v>
@@ -759,7 +759,7 @@
         <v>201</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4663</v>
+        <v>3.3744</v>
       </c>
       <c r="N7" t="n">
         <v>342</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0403</v>
+        <v>3.4239</v>
       </c>
       <c r="C8" t="n">
-        <v>0.802</v>
+        <v>0.9032</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7673</v>
+        <v>0.9077</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0403</v>
+        <v>3.4239</v>
       </c>
       <c r="F8" t="n">
-        <v>2.064</v>
+        <v>3.4239</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9762999999999999</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.064</v>
+        <v>4.1584</v>
       </c>
       <c r="I8" t="n">
-        <v>1.673</v>
+        <v>4.1584</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9762999999999999</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="L8" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6493</v>
+        <v>4.1584</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8508</v>
+        <v>3.3314</v>
       </c>
       <c r="C9" t="n">
-        <v>0.752</v>
+        <v>0.8788</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6918</v>
+        <v>0.8659</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8508</v>
+        <v>3.3314</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4111</v>
+        <v>2.543</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4397</v>
+        <v>0.7884</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4111</v>
+        <v>3.4735</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9542</v>
+        <v>1.806</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4397</v>
+        <v>0.7884</v>
       </c>
       <c r="K9" t="n">
         <v>118</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3939</v>
+        <v>2.5944</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6009</v>
+        <v>3.1539</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6861</v>
+        <v>0.832</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5923</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6009</v>
+        <v>3.1539</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6009</v>
+        <v>2.6431</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.5108</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6009</v>
+        <v>3.8264</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6009</v>
+        <v>1.9896</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.5108</v>
       </c>
       <c r="K10" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6009</v>
+        <v>2.5004</v>
       </c>
       <c r="N10" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5</v>
+        <v>3.1008</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6595</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5521</v>
+        <v>0.7618</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5</v>
+        <v>3.1008</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3479</v>
+        <v>2.5992</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1521</v>
+        <v>0.5016</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3479</v>
+        <v>3.6715</v>
       </c>
       <c r="I11" t="n">
-        <v>1.903</v>
+        <v>1.909</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1521</v>
+        <v>0.5016</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0551</v>
+        <v>2.4106</v>
       </c>
       <c r="N11" t="n">
-        <v>186</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3221</v>
+        <v>2.9838</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6126</v>
+        <v>0.7871</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4812</v>
+        <v>0.709</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3221</v>
+        <v>2.9838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3873</v>
+        <v>1.1959</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9348</v>
+        <v>1.7879</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3873</v>
+        <v>1.1959</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3139</v>
+        <v>0.6218</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9348</v>
+        <v>1.7879</v>
       </c>
       <c r="K12" t="n">
         <v>105</v>
@@ -989,7 +989,7 @@
         <v>173</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2487</v>
+        <v>2.4097</v>
       </c>
       <c r="N12" t="n">
         <v>278</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1976</v>
+        <v>2.9306</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5797</v>
+        <v>0.7731</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4316</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1976</v>
+        <v>2.9306</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0593</v>
+        <v>2.6674</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1383</v>
+        <v>0.2632</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0593</v>
+        <v>3.9121</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6692</v>
+        <v>2.0341</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1383</v>
+        <v>0.2632</v>
       </c>
       <c r="K13" t="n">
         <v>132</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8075</v>
+        <v>2.2973</v>
       </c>
       <c r="N13" t="n">
         <v>186</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1007</v>
+        <v>2.8242</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5542</v>
+        <v>0.745</v>
       </c>
       <c r="D14" t="n">
-        <v>0.393</v>
+        <v>0.637</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1007</v>
+        <v>2.8242</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1732</v>
+        <v>2.5714</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0725</v>
+        <v>0.2528</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1732</v>
+        <v>3.5737</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7614</v>
+        <v>1.8581</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0725</v>
+        <v>0.2528</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L14" t="n">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6889</v>
+        <v>2.1109</v>
       </c>
       <c r="N14" t="n">
-        <v>278</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.936</v>
+        <v>2.4102</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5107</v>
+        <v>0.6358</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3274</v>
+        <v>0.4501</v>
       </c>
       <c r="E15" t="n">
-        <v>1.936</v>
+        <v>2.4102</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4541</v>
+        <v>2.4102</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5181</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4541</v>
+        <v>2.4102</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9892</v>
+        <v>2.4102</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5181</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="L15" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4711</v>
+        <v>2.4102</v>
       </c>
       <c r="N15" t="n">
-        <v>186</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5832</v>
+        <v>2.3415</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4176</v>
+        <v>0.6177</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1868</v>
+        <v>0.4191</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5832</v>
+        <v>2.3415</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7117</v>
+        <v>1.5069</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8346</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7117</v>
+        <v>1.5069</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5768</v>
+        <v>0.7835</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8346</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4483</v>
+        <v>1.6181</v>
       </c>
       <c r="N16" t="n">
         <v>186</v>
@@ -1182,127 +1182,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4446</v>
+        <v>2.3333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3811</v>
+        <v>0.6155</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1316</v>
+        <v>0.4154</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4446</v>
+        <v>2.3333</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4446</v>
+        <v>2.6702</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.3369</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4446</v>
+        <v>3.922</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4446</v>
+        <v>2.0392</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.3369</v>
       </c>
       <c r="K17" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4446</v>
+        <v>1.7023</v>
       </c>
       <c r="N17" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4296</v>
+        <v>2.2769</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3771</v>
+        <v>0.6006</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1256</v>
+        <v>0.3899</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4296</v>
+        <v>2.2769</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4296</v>
+        <v>2.3613</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.0844</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4296</v>
+        <v>2.8335</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4296</v>
+        <v>1.4733</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.0844</v>
       </c>
       <c r="K18" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4296</v>
+        <v>1.3889</v>
       </c>
       <c r="N18" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2379</v>
+        <v>2.0421</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3266</v>
+        <v>0.5387</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0493</v>
+        <v>0.2839</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2379</v>
+        <v>2.0421</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5893</v>
+        <v>2.218</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3514</v>
+        <v>-0.1759</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5893</v>
+        <v>2.3285</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2882</v>
+        <v>1.2107</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3514</v>
+        <v>-0.1759</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>82</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9368000000000001</v>
+        <v>1.0348</v>
       </c>
       <c r="N19" t="n">
         <v>200</v>
@@ -1320,124 +1320,124 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0845</v>
+        <v>1.9443</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2861</v>
+        <v>0.5129</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0118</v>
+        <v>0.2397</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0845</v>
+        <v>1.9443</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0845</v>
+        <v>2.2249</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2806</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0845</v>
+        <v>2.3527</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0845</v>
+        <v>1.2233</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2806</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0845</v>
+        <v>0.9427000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0004</v>
+        <v>1.5442</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2639</v>
+        <v>0.4074</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0454</v>
+        <v>0.0591</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0004</v>
+        <v>1.5442</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3671</v>
+        <v>2.1656</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3667</v>
+        <v>-0.6214</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3671</v>
+        <v>2.1656</v>
       </c>
       <c r="I21" t="n">
-        <v>1.108</v>
+        <v>1.126</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3667</v>
+        <v>-0.6214</v>
       </c>
       <c r="K21" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L21" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7413000000000001</v>
+        <v>0.5045999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9571</v>
+        <v>1.4213</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2525</v>
+        <v>0.3749</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0626</v>
+        <v>0.0036</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9571</v>
+        <v>1.4213</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9571</v>
+        <v>1.4213</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9571</v>
+        <v>1.4213</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9571</v>
+        <v>1.4213</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9571</v>
+        <v>1.4213</v>
       </c>
       <c r="N22" t="n">
         <v>111</v>
@@ -1458,829 +1458,829 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8158</v>
+        <v>1.2526</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2152</v>
+        <v>0.3304</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1189</v>
+        <v>-0.0725</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8158</v>
+        <v>1.2526</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8158</v>
+        <v>1.2526</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8158</v>
+        <v>1.2526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8158</v>
+        <v>1.2526</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8158</v>
+        <v>1.2526</v>
       </c>
       <c r="N23" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5302</v>
+        <v>1.0849</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1399</v>
+        <v>0.2862</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2327</v>
+        <v>-0.1482</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5302</v>
+        <v>1.0849</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1923</v>
+        <v>1.0849</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1923</v>
+        <v>1.0849</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9664</v>
+        <v>1.0849</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L24" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3043</v>
+        <v>1.0849</v>
       </c>
       <c r="N24" t="n">
-        <v>200</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3205</v>
+        <v>0.9566</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.2523</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3162</v>
+        <v>-0.2062</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3205</v>
+        <v>0.9566</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3205</v>
+        <v>0.9566</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3205</v>
+        <v>0.9566</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3205</v>
+        <v>0.9566</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3205</v>
+        <v>0.9566</v>
       </c>
       <c r="N25" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1654</v>
+        <v>0.4253</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0436</v>
+        <v>0.1122</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.378</v>
+        <v>-0.446</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1654</v>
+        <v>0.4253</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1343</v>
+        <v>0.4253</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9689</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1343</v>
+        <v>0.4253</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9194</v>
+        <v>0.4253</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9689</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L26" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.04949999999999999</v>
+        <v>0.4253</v>
       </c>
       <c r="N26" t="n">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1037</v>
+        <v>0.3281</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0274</v>
+        <v>0.0866</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4026</v>
+        <v>-0.4899</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1037</v>
+        <v>0.3281</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1037</v>
+        <v>0.3281</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1037</v>
+        <v>0.3281</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1037</v>
+        <v>0.3281</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1037</v>
+        <v>0.3281</v>
       </c>
       <c r="N27" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0697</v>
+        <v>0.1312</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0184</v>
+        <v>0.0346</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4161</v>
+        <v>-0.5788</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0697</v>
+        <v>0.1312</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0697</v>
+        <v>0.1312</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0697</v>
+        <v>0.1312</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0697</v>
+        <v>0.1312</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0697</v>
+        <v>0.1312</v>
       </c>
       <c r="N28" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2144</v>
+        <v>0.0804</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0566</v>
+        <v>0.0212</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5293</v>
+        <v>-0.6017</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2144</v>
+        <v>0.0804</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2144</v>
+        <v>0.0804</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2144</v>
+        <v>0.0804</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2144</v>
+        <v>0.0804</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2144</v>
+        <v>0.0804</v>
       </c>
       <c r="N29" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3545</v>
+        <v>0.0246</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0935</v>
+        <v>0.0065</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5851</v>
+        <v>-0.6269</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3545</v>
+        <v>0.0246</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3545</v>
+        <v>0.0246</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3545</v>
+        <v>0.0246</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3545</v>
+        <v>0.0246</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3545</v>
+        <v>0.0246</v>
       </c>
       <c r="N30" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4875</v>
+        <v>-0.1884</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1286</v>
+        <v>-0.0497</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6381</v>
+        <v>-0.7231</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4875</v>
+        <v>-0.1884</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4875</v>
+        <v>-0.1884</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4875</v>
+        <v>-0.1884</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4875</v>
+        <v>-0.1884</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4875</v>
+        <v>-0.1884</v>
       </c>
       <c r="N31" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5031</v>
+        <v>-0.2416</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1327</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6443</v>
+        <v>-0.7471</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5031</v>
+        <v>-0.2416</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5031</v>
+        <v>-0.2416</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5031</v>
+        <v>-0.2416</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5031</v>
+        <v>-0.2416</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5031</v>
+        <v>-0.2416</v>
       </c>
       <c r="N32" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9123</v>
+        <v>-0.3773</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2407</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8074</v>
+        <v>-0.8083</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9123</v>
+        <v>-0.3773</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9123</v>
+        <v>-0.3773</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9123</v>
+        <v>-0.3773</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9123</v>
+        <v>-0.3773</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9123</v>
+        <v>-0.3773</v>
       </c>
       <c r="N33" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.006</v>
+        <v>-0.6469</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2654</v>
+        <v>-0.1706</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8447</v>
+        <v>-0.9301</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.006</v>
+        <v>-0.6469</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.006</v>
+        <v>-0.6469</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.006</v>
+        <v>-0.6469</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.006</v>
+        <v>-0.6469</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.006</v>
+        <v>-0.6469</v>
       </c>
       <c r="N34" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1379</v>
+        <v>-0.7035</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3002</v>
+        <v>-0.1856</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8972</v>
+        <v>-0.9556</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1379</v>
+        <v>-0.7035</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.0146</v>
+        <v>-0.7035</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8767</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-2.0146</v>
+        <v>-0.7035</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.6329</v>
+        <v>-0.7035</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8767</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="L35" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7562</v>
+        <v>-0.7035</v>
       </c>
       <c r="N35" t="n">
-        <v>342</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1659</v>
+        <v>-0.9369</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3076</v>
+        <v>-0.2471</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9084</v>
+        <v>-1.061</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1659</v>
+        <v>-0.9369</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1659</v>
+        <v>-0.9369</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1659</v>
+        <v>-0.9369</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1659</v>
+        <v>-0.9369</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1659</v>
+        <v>-0.9369</v>
       </c>
       <c r="N36" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.393</v>
+        <v>-1.1028</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3675</v>
+        <v>-0.2909</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9989</v>
+        <v>-1.1359</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.393</v>
+        <v>-1.1028</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.393</v>
+        <v>-2.2823</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.1795</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.393</v>
+        <v>-2.2823</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.393</v>
+        <v>-1.1867</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1.1795</v>
       </c>
       <c r="K37" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.393</v>
+        <v>-0.007200000000000095</v>
       </c>
       <c r="N37" t="n">
-        <v>70</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4055</v>
+        <v>-1.145</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3708</v>
+        <v>-0.302</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0039</v>
+        <v>-1.1549</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4055</v>
+        <v>-1.145</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4055</v>
+        <v>-1.145</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4055</v>
+        <v>-1.145</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4055</v>
+        <v>-1.145</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4055</v>
+        <v>-1.145</v>
       </c>
       <c r="N38" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6528</v>
+        <v>-1.213</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.436</v>
+        <v>-0.32</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1024</v>
+        <v>-1.1856</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6528</v>
+        <v>-1.213</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6528</v>
+        <v>-1.213</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6528</v>
+        <v>-1.213</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6528</v>
+        <v>-1.213</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6528</v>
+        <v>-1.213</v>
       </c>
       <c r="N39" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7672</v>
+        <v>-1.2454</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4662</v>
+        <v>-0.3285</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.148</v>
+        <v>-1.2003</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7672</v>
+        <v>-1.2454</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7672</v>
+        <v>-1.2454</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7672</v>
+        <v>-1.2454</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7672</v>
+        <v>-1.2454</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7672</v>
+        <v>-1.2454</v>
       </c>
       <c r="N40" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7612</v>
+        <v>-2.2992</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7284</v>
+        <v>-0.6065</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.544</v>
+        <v>-1.676</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7612</v>
+        <v>-2.2992</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7612</v>
+        <v>-0.5897</v>
       </c>
       <c r="G41" t="n">
-        <v>-2</v>
+        <v>-1.7095</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7612</v>
+        <v>-0.5897</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.617</v>
+        <v>-0.3066</v>
       </c>
       <c r="J41" t="n">
-        <v>-2</v>
+        <v>-1.7095</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>173</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.617</v>
+        <v>-2.0161</v>
       </c>
       <c r="N41" t="n">
         <v>278</v>
@@ -2429,10 +2429,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3711</v>
+        <v>1.251</v>
       </c>
       <c r="J2" t="n">
-        <v>32.9064</v>
+        <v>30.024</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1947</v>
+        <v>1.1429</v>
       </c>
       <c r="J3" t="n">
-        <v>28.6728</v>
+        <v>27.4296</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8541</v>
+        <v>0.931</v>
       </c>
       <c r="J4" t="n">
-        <v>20.4984</v>
+        <v>22.344</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.8041</v>
       </c>
       <c r="J5" t="n">
-        <v>16.9224</v>
+        <v>19.2984</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0541</v>
+        <v>0.1417</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2984</v>
+        <v>3.4008</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.17</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4247</v>
+        <v>0.4833</v>
       </c>
       <c r="J7" t="n">
-        <v>10.1928</v>
+        <v>11.5992</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.86</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1799</v>
+        <v>-0.1518</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.3176</v>
+        <v>-3.6432</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3823</v>
+        <v>-0.2601</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.1752</v>
+        <v>-6.2424</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.57</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6413</v>
+        <v>-0.4295</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.3912</v>
+        <v>-10.308</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.68</v>
+        <v>-0.4574</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.32</v>
+        <v>-10.9776</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.209</v>
+        <v>-0.1852</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.389</v>
+        <v>-3.8892</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2874</v>
+        <v>-0.2384</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.0354</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5951</v>
+        <v>-0.4073</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.4971</v>
+        <v>-8.5533</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6244</v>
+        <v>-0.4259</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.1124</v>
+        <v>-8.943899999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.54</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6387</v>
+        <v>-0.4353</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.4127</v>
+        <v>-9.141299999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0211</v>
+        <v>0.9419</v>
       </c>
       <c r="J17" t="n">
-        <v>21.4431</v>
+        <v>19.7799</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.76</v>
       </c>
       <c r="I18" t="n">
-        <v>0.92</v>
+        <v>0.8465</v>
       </c>
       <c r="J18" t="n">
-        <v>19.32</v>
+        <v>17.7765</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.43</v>
       </c>
       <c r="I19" t="n">
-        <v>0.53</v>
+        <v>0.5162</v>
       </c>
       <c r="J19" t="n">
-        <v>11.13</v>
+        <v>10.8402</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2302</v>
+        <v>0.2562</v>
       </c>
       <c r="J20" t="n">
-        <v>4.8342</v>
+        <v>5.3802</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1108</v>
+        <v>-0.0405</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3268</v>
+        <v>-0.8505</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0499</v>
+        <v>1.0237</v>
       </c>
       <c r="J22" t="n">
-        <v>26.2475</v>
+        <v>25.5925</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4443</v>
+        <v>0.4481</v>
       </c>
       <c r="J23" t="n">
-        <v>11.1075</v>
+        <v>11.2025</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.13</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3721</v>
+        <v>0.3975</v>
       </c>
       <c r="J24" t="n">
-        <v>9.3025</v>
+        <v>9.9375</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3384</v>
+        <v>0.3715</v>
       </c>
       <c r="J25" t="n">
-        <v>8.460000000000001</v>
+        <v>9.2875</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5366</v>
+        <v>-0.4715</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.415</v>
+        <v>-11.7875</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.02</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1014</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>2.535</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1014</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>2.535</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.076</v>
+        <v>0.0523</v>
       </c>
       <c r="J29" t="n">
-        <v>1.9</v>
+        <v>1.3075</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3647</v>
+        <v>-0.2304</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.1175</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3795</v>
+        <v>-0.2403</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.487500000000001</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.45</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6964</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>20.1956</v>
+        <v>19.0472</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1621</v>
+        <v>0.1361</v>
       </c>
       <c r="J33" t="n">
-        <v>4.7009</v>
+        <v>3.9469</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1041</v>
+        <v>-0.0527</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.0189</v>
+        <v>-1.5283</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1838</v>
+        <v>-0.103</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.3302</v>
+        <v>-2.987</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4991</v>
+        <v>-0.3203</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.4739</v>
+        <v>-9.2887</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6337</v>
+        <v>0.5556</v>
       </c>
       <c r="J37" t="n">
-        <v>18.3773</v>
+        <v>16.1124</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2614</v>
+        <v>0.2363</v>
       </c>
       <c r="J38" t="n">
-        <v>7.5806</v>
+        <v>6.8527</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.239</v>
+        <v>0.224</v>
       </c>
       <c r="J39" t="n">
-        <v>6.931</v>
+        <v>6.496</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2201</v>
+        <v>0.2113</v>
       </c>
       <c r="J40" t="n">
-        <v>6.3829</v>
+        <v>6.1277</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2812</v>
+        <v>-0.1618</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.1548</v>
+        <v>-4.6922</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.38</v>
       </c>
       <c r="I42" t="n">
-        <v>2.3055</v>
+        <v>1.8681</v>
       </c>
       <c r="J42" t="n">
-        <v>46.11</v>
+        <v>37.362</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9781</v>
+        <v>1.049</v>
       </c>
       <c r="J43" t="n">
-        <v>19.562</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7972</v>
+        <v>0.9175</v>
       </c>
       <c r="J44" t="n">
-        <v>15.944</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2485</v>
+        <v>0.3513</v>
       </c>
       <c r="J45" t="n">
-        <v>4.97</v>
+        <v>7.026</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1974</v>
+        <v>-0.1095</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.948</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1964</v>
+        <v>-0.176</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.928</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2122</v>
+        <v>-0.187</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.244</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.64</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4842</v>
+        <v>-0.3445</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.683999999999999</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.59</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5678</v>
+        <v>-0.3898</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.356</v>
+        <v>-7.796</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.4</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8267</v>
+        <v>-0.5682</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.534</v>
+        <v>-11.364</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.03</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1493</v>
+        <v>0.128</v>
       </c>
       <c r="J52" t="n">
-        <v>3.7325</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1922</v>
+        <v>-0.1427</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.805</v>
+        <v>-3.5675</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2129</v>
+        <v>-0.1529</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.3225</v>
+        <v>-3.8225</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2937</v>
+        <v>-0.1928</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.3425</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4625</v>
+        <v>-0.3006</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.5625</v>
+        <v>-7.515</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1388</v>
+        <v>1.0928</v>
       </c>
       <c r="J57" t="n">
-        <v>28.47</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5664</v>
+        <v>0.6239</v>
       </c>
       <c r="J58" t="n">
-        <v>14.16</v>
+        <v>15.5975</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6005</v>
       </c>
       <c r="J59" t="n">
-        <v>13.47</v>
+        <v>15.0125</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.17</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4058</v>
+        <v>0.4784</v>
       </c>
       <c r="J60" t="n">
-        <v>10.145</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.14</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3258</v>
+        <v>0.4009</v>
       </c>
       <c r="J61" t="n">
-        <v>8.145</v>
+        <v>10.0225</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.67</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8709</v>
+        <v>0.7896</v>
       </c>
       <c r="J62" t="n">
-        <v>20.0307</v>
+        <v>18.1608</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5627</v>
+        <v>0.5018</v>
       </c>
       <c r="J63" t="n">
-        <v>12.9421</v>
+        <v>11.5414</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.35</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4985</v>
+        <v>0.4466</v>
       </c>
       <c r="J64" t="n">
-        <v>11.4655</v>
+        <v>10.2718</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1177</v>
+        <v>-0.0464</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.7071</v>
+        <v>-1.0672</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2188</v>
+        <v>-0.1153</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.0324</v>
+        <v>-2.6519</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.15</v>
       </c>
       <c r="I67" t="n">
-        <v>0.354</v>
+        <v>0.2976</v>
       </c>
       <c r="J67" t="n">
-        <v>8.141999999999999</v>
+        <v>6.8448</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1805</v>
+        <v>-0.1333</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.1515</v>
+        <v>-3.0659</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.0017</v>
+        <v>-5.1543</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3787</v>
+        <v>-0.2439</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.710100000000001</v>
+        <v>-5.6097</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3937</v>
+        <v>-0.2537</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.055099999999999</v>
+        <v>-5.8351</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.04</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2032</v>
+        <v>0.1883</v>
       </c>
       <c r="J72" t="n">
-        <v>4.4704</v>
+        <v>4.1426</v>
       </c>
     </row>
     <row r="73">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2886</v>
+        <v>-0.2144</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.3492</v>
+        <v>-4.7168</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4644</v>
+        <v>-0.3085</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.2168</v>
+        <v>-6.787</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.48</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7564</v>
+        <v>-0.514</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.6408</v>
+        <v>-11.308</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.7986</v>
+        <v>1.5276</v>
       </c>
       <c r="J77" t="n">
-        <v>39.5692</v>
+        <v>33.6072</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.35</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7971</v>
+        <v>0.8731</v>
       </c>
       <c r="J78" t="n">
-        <v>17.5362</v>
+        <v>19.2082</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.35</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7971</v>
+        <v>0.8731</v>
       </c>
       <c r="J79" t="n">
-        <v>17.5362</v>
+        <v>19.2082</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7702</v>
+        <v>0.8519</v>
       </c>
       <c r="J80" t="n">
-        <v>16.9444</v>
+        <v>18.7418</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.542</v>
+        <v>-0.4678</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.924</v>
+        <v>-10.2916</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6837</v>
+        <v>0.6324</v>
       </c>
       <c r="J82" t="n">
-        <v>19.1436</v>
+        <v>17.7072</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.736</v>
+        <v>-1.3216</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2975</v>
+        <v>-0.1833</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.33</v>
+        <v>-5.1324</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2975</v>
+        <v>-0.1833</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.33</v>
+        <v>-5.1324</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4993</v>
+        <v>-0.3221</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.9804</v>
+        <v>-9.018800000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.45</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1378</v>
+        <v>0.8114</v>
       </c>
       <c r="J87" t="n">
-        <v>31.8584</v>
+        <v>22.7192</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.26</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7163</v>
+        <v>0.5553</v>
       </c>
       <c r="J88" t="n">
-        <v>20.0564</v>
+        <v>15.5484</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.14</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3728</v>
+        <v>0.3835</v>
       </c>
       <c r="J89" t="n">
-        <v>10.4384</v>
+        <v>10.738</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.7292</v>
+        <v>-2.6572</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.7292</v>
+        <v>-2.6572</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.25</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4496</v>
+        <v>0.4465</v>
       </c>
       <c r="J92" t="n">
-        <v>11.6896</v>
+        <v>11.609</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4358</v>
+        <v>0.4361</v>
       </c>
       <c r="J93" t="n">
-        <v>11.3308</v>
+        <v>11.3386</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1878</v>
+        <v>0.2022</v>
       </c>
       <c r="J94" t="n">
-        <v>4.8828</v>
+        <v>5.2572</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4561</v>
+        <v>-0.2897</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.8586</v>
+        <v>-7.5322</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.74</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4696</v>
+        <v>-0.2993</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.2096</v>
+        <v>-7.7818</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.6498</v>
       </c>
       <c r="J97" t="n">
-        <v>23.2882</v>
+        <v>16.8948</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.13</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4459</v>
+        <v>0.3815</v>
       </c>
       <c r="J98" t="n">
-        <v>11.5934</v>
+        <v>9.919</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4169</v>
+        <v>0.3654</v>
       </c>
       <c r="J99" t="n">
-        <v>10.8394</v>
+        <v>9.500400000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3872</v>
+        <v>0.3489</v>
       </c>
       <c r="J100" t="n">
-        <v>10.0672</v>
+        <v>9.071400000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.61</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.1159</v>
+        <v>-1.1062</v>
       </c>
       <c r="J101" t="n">
-        <v>-29.0134</v>
+        <v>-28.7612</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.43</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6408</v>
+        <v>0.4677</v>
       </c>
       <c r="J102" t="n">
-        <v>19.224</v>
+        <v>14.031</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.26</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4239</v>
+        <v>0.3506</v>
       </c>
       <c r="J103" t="n">
-        <v>12.717</v>
+        <v>10.518</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2395</v>
+        <v>0.2129</v>
       </c>
       <c r="J104" t="n">
-        <v>7.185</v>
+        <v>6.387</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0673</v>
+        <v>0.0853</v>
       </c>
       <c r="J105" t="n">
-        <v>2.019</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4497</v>
+        <v>-0.2827</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.491</v>
+        <v>-8.481</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5322</v>
+        <v>0.4241</v>
       </c>
       <c r="J107" t="n">
-        <v>15.966</v>
+        <v>12.723</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5063</v>
+        <v>0.4087</v>
       </c>
       <c r="J108" t="n">
-        <v>15.189</v>
+        <v>12.261</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1133</v>
+        <v>0.1013</v>
       </c>
       <c r="J109" t="n">
-        <v>3.399</v>
+        <v>3.039</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0366</v>
+        <v>0.0466</v>
       </c>
       <c r="J110" t="n">
-        <v>1.098</v>
+        <v>1.398</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.52</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7454</v>
+        <v>-0.5053</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.362</v>
+        <v>-15.159</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2956</v>
+        <v>0.3115</v>
       </c>
       <c r="J112" t="n">
-        <v>6.5032</v>
+        <v>6.853</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1702</v>
+        <v>0.1535</v>
       </c>
       <c r="J113" t="n">
-        <v>3.7444</v>
+        <v>3.377</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.85</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2579</v>
+        <v>-0.1728</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.6738</v>
+        <v>-3.8016</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4046</v>
+        <v>-0.2619</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.901199999999999</v>
+        <v>-5.7618</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.57</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6606</v>
+        <v>-0.4415</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.5332</v>
+        <v>-9.712999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.76</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6482</v>
+        <v>1.1534</v>
       </c>
       <c r="J117" t="n">
-        <v>36.2604</v>
+        <v>25.3748</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8965</v>
+        <v>0.6904</v>
       </c>
       <c r="J118" t="n">
-        <v>19.723</v>
+        <v>15.1888</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4649</v>
+        <v>0.4662</v>
       </c>
       <c r="J119" t="n">
-        <v>10.2278</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3658</v>
+        <v>0.4074</v>
       </c>
       <c r="J120" t="n">
-        <v>8.047599999999999</v>
+        <v>8.9628</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.16</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3406</v>
+        <v>0.3923</v>
       </c>
       <c r="J121" t="n">
-        <v>7.4932</v>
+        <v>8.630599999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4482</v>
+        <v>0.4436</v>
       </c>
       <c r="J122" t="n">
-        <v>13.446</v>
+        <v>13.308</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4204</v>
+        <v>0.4221</v>
       </c>
       <c r="J123" t="n">
-        <v>12.612</v>
+        <v>12.663</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1653</v>
+        <v>0.1672</v>
       </c>
       <c r="J124" t="n">
-        <v>4.959</v>
+        <v>5.016</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3483</v>
+        <v>-0.216</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.449</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7143</v>
+        <v>-0.4812</v>
       </c>
       <c r="J126" t="n">
-        <v>-21.429</v>
+        <v>-14.436</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.69</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6131</v>
+        <v>1.1251</v>
       </c>
       <c r="J127" t="n">
-        <v>48.393</v>
+        <v>33.753</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6804</v>
+        <v>0.5309</v>
       </c>
       <c r="J128" t="n">
-        <v>20.412</v>
+        <v>15.927</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6301</v>
+        <v>0.5024</v>
       </c>
       <c r="J129" t="n">
-        <v>18.903</v>
+        <v>15.072</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.87</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.4741</v>
       </c>
       <c r="J130" t="n">
-        <v>-16.194</v>
+        <v>-14.223</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9435</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>-28.305</v>
+        <v>-27.354</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.67</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4435</v>
+        <v>1.3013</v>
       </c>
       <c r="J132" t="n">
-        <v>28.87</v>
+        <v>26.026</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1493</v>
+        <v>1.124</v>
       </c>
       <c r="J133" t="n">
-        <v>22.986</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.45</v>
       </c>
       <c r="I134" t="n">
-        <v>0.995</v>
+        <v>1.0391</v>
       </c>
       <c r="J134" t="n">
-        <v>19.9</v>
+        <v>20.782</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.37</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7941</v>
+        <v>0.9036</v>
       </c>
       <c r="J135" t="n">
-        <v>15.882</v>
+        <v>18.072</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.15</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2844</v>
+        <v>0.386</v>
       </c>
       <c r="J136" t="n">
-        <v>5.688</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0315</v>
+        <v>-0.0582</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.63</v>
+        <v>-1.164</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.68</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3824</v>
+        <v>-0.3027</v>
       </c>
       <c r="J138" t="n">
-        <v>-7.648</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.6273</v>
+        <v>-0.4305</v>
       </c>
       <c r="J139" t="n">
-        <v>-12.546</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.5</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6849</v>
+        <v>-0.468</v>
       </c>
       <c r="J140" t="n">
-        <v>-13.698</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7399</v>
+        <v>-0.5058</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.798</v>
+        <v>-10.116</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>1.493</v>
+        <v>1.3175</v>
       </c>
       <c r="J142" t="n">
-        <v>43.297</v>
+        <v>38.2075</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1351</v>
+        <v>0.154</v>
       </c>
       <c r="J143" t="n">
-        <v>3.9179</v>
+        <v>4.466</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0537</v>
+        <v>0.0837</v>
       </c>
       <c r="J144" t="n">
-        <v>1.5573</v>
+        <v>2.4273</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0528</v>
+        <v>-0.0112</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.5312</v>
+        <v>-0.3248</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.1155</v>
+        <v>-1.1057</v>
       </c>
       <c r="J146" t="n">
-        <v>-32.3495</v>
+        <v>-32.0653</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.8629</v>
       </c>
       <c r="J147" t="n">
-        <v>20.2739</v>
+        <v>25.0241</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.09</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1868</v>
+        <v>0.2143</v>
       </c>
       <c r="J148" t="n">
-        <v>5.4172</v>
+        <v>6.2147</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0994</v>
+        <v>0.1311</v>
       </c>
       <c r="J149" t="n">
-        <v>2.8826</v>
+        <v>3.8019</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.84</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3377</v>
+        <v>-0.2047</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.7933</v>
+        <v>-5.9363</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.84</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3377</v>
+        <v>-0.2047</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.7933</v>
+        <v>-5.9363</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.18</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3223</v>
+        <v>0.3783</v>
       </c>
       <c r="J152" t="n">
-        <v>9.669</v>
+        <v>11.349</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2913</v>
+        <v>0.3419</v>
       </c>
       <c r="J153" t="n">
-        <v>8.739000000000001</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1421</v>
+        <v>0.1902</v>
       </c>
       <c r="J154" t="n">
-        <v>4.263</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1019</v>
+        <v>0.1484</v>
       </c>
       <c r="J155" t="n">
-        <v>3.057</v>
+        <v>4.452</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1242</v>
+        <v>-0.059</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.726</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.53</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3253</v>
+        <v>1.2044</v>
       </c>
       <c r="J157" t="n">
-        <v>39.759</v>
+        <v>36.132</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4009</v>
+        <v>0.4002</v>
       </c>
       <c r="J158" t="n">
-        <v>12.027</v>
+        <v>12.006</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3678</v>
+        <v>0.3741</v>
       </c>
       <c r="J159" t="n">
-        <v>11.034</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0914</v>
+        <v>0.1405</v>
       </c>
       <c r="J160" t="n">
-        <v>2.742</v>
+        <v>4.215</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8244</v>
+        <v>-0.7809</v>
       </c>
       <c r="J161" t="n">
-        <v>-24.732</v>
+        <v>-23.427</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.05</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1669</v>
+        <v>0.1584</v>
       </c>
       <c r="J162" t="n">
-        <v>5.007</v>
+        <v>4.752</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.02</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1031</v>
+        <v>0.0827</v>
       </c>
       <c r="J163" t="n">
-        <v>3.093</v>
+        <v>2.481</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.86</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2686</v>
+        <v>-0.1687</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.058</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.86</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2686</v>
+        <v>-0.1687</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.058</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3173</v>
+        <v>-0.1996</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.519</v>
+        <v>-5.988</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.57</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3188</v>
+        <v>1.2096</v>
       </c>
       <c r="J167" t="n">
-        <v>39.564</v>
+        <v>36.288</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.32</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.8185</v>
       </c>
       <c r="J168" t="n">
-        <v>23.574</v>
+        <v>24.555</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7343</v>
+        <v>0.7746</v>
       </c>
       <c r="J169" t="n">
-        <v>22.029</v>
+        <v>23.238</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.27</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6428</v>
+        <v>0.709</v>
       </c>
       <c r="J170" t="n">
-        <v>19.284</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2877</v>
+        <v>-0.2029</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.631</v>
+        <v>-6.087</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.23</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4738</v>
+        <v>0.4203</v>
       </c>
       <c r="J172" t="n">
-        <v>11.3712</v>
+        <v>10.0872</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.311</v>
+        <v>0.2541</v>
       </c>
       <c r="J173" t="n">
-        <v>7.464</v>
+        <v>6.0984</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.101</v>
+        <v>0.0537</v>
       </c>
       <c r="J174" t="n">
-        <v>2.424</v>
+        <v>1.2888</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7343</v>
+        <v>-0.4967</v>
       </c>
       <c r="J175" t="n">
-        <v>-17.6232</v>
+        <v>-11.9208</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.47</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.5331</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.7632</v>
+        <v>-12.7944</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.62</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8004</v>
+        <v>0.7252</v>
       </c>
       <c r="J177" t="n">
-        <v>19.2096</v>
+        <v>17.4048</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5679</v>
+        <v>0.5153</v>
       </c>
       <c r="J178" t="n">
-        <v>13.6296</v>
+        <v>12.3672</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.39</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5293</v>
+        <v>0.4832</v>
       </c>
       <c r="J179" t="n">
-        <v>12.7032</v>
+        <v>11.5968</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.25</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3236</v>
+        <v>0.329</v>
       </c>
       <c r="J180" t="n">
-        <v>7.7664</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1281</v>
+        <v>-0.0521</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.0744</v>
+        <v>-1.2504</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5711</v>
+        <v>1.3766</v>
       </c>
       <c r="J182" t="n">
-        <v>36.1353</v>
+        <v>31.6618</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.68</v>
       </c>
       <c r="I183" t="n">
-        <v>1.4978</v>
+        <v>1.329</v>
       </c>
       <c r="J183" t="n">
-        <v>34.4494</v>
+        <v>30.567</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.17</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3606</v>
+        <v>0.4555</v>
       </c>
       <c r="J184" t="n">
-        <v>8.293799999999999</v>
+        <v>10.4765</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2321</v>
+        <v>0.3234</v>
       </c>
       <c r="J185" t="n">
-        <v>5.3383</v>
+        <v>7.4382</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.063</v>
+        <v>0.1487</v>
       </c>
       <c r="J186" t="n">
-        <v>1.449</v>
+        <v>3.4201</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2487</v>
+        <v>0.2465</v>
       </c>
       <c r="J187" t="n">
-        <v>5.7201</v>
+        <v>5.6695</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0304</v>
       </c>
       <c r="J188" t="n">
-        <v>1.6882</v>
+        <v>0.6992</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.64</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.3628</v>
       </c>
       <c r="J189" t="n">
-        <v>-12.5327</v>
+        <v>-8.3444</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.63</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5587</v>
+        <v>-0.3722</v>
       </c>
       <c r="J190" t="n">
-        <v>-12.8501</v>
+        <v>-8.560600000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6908</v>
+        <v>-0.4655</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.8884</v>
+        <v>-10.7065</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.64</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4859</v>
+        <v>1.3142</v>
       </c>
       <c r="J192" t="n">
-        <v>32.6898</v>
+        <v>28.9124</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.32</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8305</v>
+        <v>0.8354</v>
       </c>
       <c r="J193" t="n">
-        <v>18.271</v>
+        <v>18.3788</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6058</v>
+        <v>0.628</v>
       </c>
       <c r="J194" t="n">
-        <v>13.3276</v>
+        <v>13.816</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.16</v>
       </c>
       <c r="I195" t="n">
-        <v>0.397</v>
+        <v>0.4598</v>
       </c>
       <c r="J195" t="n">
-        <v>8.734</v>
+        <v>10.1156</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9147</v>
+        <v>-0.879</v>
       </c>
       <c r="J196" t="n">
-        <v>-20.1234</v>
+        <v>-19.338</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3025</v>
+        <v>0.3229</v>
       </c>
       <c r="J197" t="n">
-        <v>6.655</v>
+        <v>7.1038</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.9558</v>
+        <v>-1.716</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.288</v>
+        <v>-0.1854</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.336</v>
+        <v>-4.0788</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3676</v>
+        <v>-0.2355</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.087199999999999</v>
+        <v>-5.181</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4123</v>
+        <v>-0.265</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.070600000000001</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3912</v>
+        <v>0.4369</v>
       </c>
       <c r="J202" t="n">
-        <v>8.9976</v>
+        <v>10.0487</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.9</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1147</v>
+        <v>-0.1086</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.6381</v>
+        <v>-2.4978</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.37</v>
+        <v>-0.2517</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.51</v>
+        <v>-5.7891</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5221</v>
+        <v>-0.3463</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.0083</v>
+        <v>-7.9649</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.46</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.5324</v>
       </c>
       <c r="J206" t="n">
-        <v>-17.9561</v>
+        <v>-12.2452</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.83</v>
       </c>
       <c r="I207" t="n">
-        <v>1.7528</v>
+        <v>1.4979</v>
       </c>
       <c r="J207" t="n">
-        <v>40.3144</v>
+        <v>34.4517</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1947</v>
+        <v>1.143</v>
       </c>
       <c r="J208" t="n">
-        <v>27.4781</v>
+        <v>26.289</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5884</v>
+        <v>0.6911</v>
       </c>
       <c r="J209" t="n">
-        <v>13.5332</v>
+        <v>15.8953</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.15</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2994</v>
+        <v>0.3967</v>
       </c>
       <c r="J210" t="n">
-        <v>6.8862</v>
+        <v>9.1241</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.13</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2482</v>
+        <v>0.3435</v>
       </c>
       <c r="J211" t="n">
-        <v>5.7086</v>
+        <v>7.9005</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1657</v>
+        <v>0.1437</v>
       </c>
       <c r="J212" t="n">
-        <v>3.9768</v>
+        <v>3.4488</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0493</v>
+        <v>0.006</v>
       </c>
       <c r="J213" t="n">
-        <v>1.1832</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0784</v>
+        <v>-0.0805</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.8816</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.601</v>
+        <v>-0.3991</v>
       </c>
       <c r="J215" t="n">
-        <v>-14.424</v>
+        <v>-9.5784</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.57</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6525</v>
+        <v>-0.4363</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.66</v>
+        <v>-10.4712</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5604</v>
+        <v>1.3666</v>
       </c>
       <c r="J217" t="n">
-        <v>37.4496</v>
+        <v>32.7984</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.68</v>
       </c>
       <c r="I218" t="n">
-        <v>1.5238</v>
+        <v>1.3425</v>
       </c>
       <c r="J218" t="n">
-        <v>36.5712</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.18</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4093</v>
+        <v>0.4936</v>
       </c>
       <c r="J219" t="n">
-        <v>9.8232</v>
+        <v>11.8464</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3234</v>
+        <v>-0.2393</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.7616</v>
+        <v>-5.7432</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3866</v>
+        <v>-0.3048</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.2784</v>
+        <v>-7.3152</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.09</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2498</v>
+        <v>0.2566</v>
       </c>
       <c r="J222" t="n">
-        <v>6.9944</v>
+        <v>7.1848</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1138</v>
+        <v>0.0902</v>
       </c>
       <c r="J223" t="n">
-        <v>3.1864</v>
+        <v>2.5256</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.84</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2914</v>
+        <v>-0.1863</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.1592</v>
+        <v>-5.2164</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.79</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3703</v>
+        <v>-0.2366</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.3684</v>
+        <v>-6.6248</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4291</v>
+        <v>-0.2758</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.0148</v>
+        <v>-7.7224</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.61</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4411</v>
+        <v>1.2836</v>
       </c>
       <c r="J227" t="n">
-        <v>40.3508</v>
+        <v>35.9408</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7014</v>
+        <v>0.7033</v>
       </c>
       <c r="J228" t="n">
-        <v>19.6392</v>
+        <v>19.6924</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2413</v>
+        <v>0.3048</v>
       </c>
       <c r="J229" t="n">
-        <v>6.7564</v>
+        <v>8.5344</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1513</v>
+        <v>0.2173</v>
       </c>
       <c r="J230" t="n">
-        <v>4.2364</v>
+        <v>6.0844</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4452</v>
+        <v>-0.3717</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.4656</v>
+        <v>-10.4076</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.36</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9371</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J232" t="n">
-        <v>31.8614</v>
+        <v>31.756</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.22</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6027</v>
+        <v>0.6101</v>
       </c>
       <c r="J233" t="n">
-        <v>20.4918</v>
+        <v>20.7434</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3886</v>
+        <v>0.4403</v>
       </c>
       <c r="J234" t="n">
-        <v>13.2124</v>
+        <v>14.9702</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.14</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3599</v>
+        <v>0.4145</v>
       </c>
       <c r="J235" t="n">
-        <v>12.2366</v>
+        <v>14.093</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1563</v>
       </c>
       <c r="J236" t="n">
-        <v>3.0736</v>
+        <v>5.3142</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.2</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4056</v>
+        <v>0.4608</v>
       </c>
       <c r="J237" t="n">
-        <v>13.7904</v>
+        <v>15.6672</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0364</v>
+        <v>0.0109</v>
       </c>
       <c r="J238" t="n">
-        <v>1.2376</v>
+        <v>0.3706</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.86</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2739</v>
+        <v>-0.1703</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.3126</v>
+        <v>-5.7902</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3062</v>
+        <v>-0.191</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.4108</v>
+        <v>-6.494</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3824</v>
+        <v>-0.2416</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.0016</v>
+        <v>-8.214399999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.7</v>
       </c>
       <c r="I242" t="n">
-        <v>1.5311</v>
+        <v>1.3511</v>
       </c>
       <c r="J242" t="n">
-        <v>35.2153</v>
+        <v>31.0753</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.69</v>
       </c>
       <c r="I243" t="n">
-        <v>1.5127</v>
+        <v>1.3392</v>
       </c>
       <c r="J243" t="n">
-        <v>34.7921</v>
+        <v>30.8016</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.43</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9967</v>
+        <v>1.0201</v>
       </c>
       <c r="J244" t="n">
-        <v>22.9241</v>
+        <v>23.4623</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.3074</v>
+        <v>0.402</v>
       </c>
       <c r="J245" t="n">
-        <v>7.0702</v>
+        <v>9.246</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6576</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.4726</v>
+        <v>-15.1248</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.89</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.12</v>
+        <v>-0.1148</v>
       </c>
       <c r="J247" t="n">
-        <v>-2.76</v>
+        <v>-2.6404</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.73</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4055</v>
+        <v>-0.2767</v>
       </c>
       <c r="J248" t="n">
-        <v>-9.326499999999999</v>
+        <v>-6.3641</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4055</v>
+        <v>-0.2767</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.326499999999999</v>
+        <v>-6.3641</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.73</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4055</v>
+        <v>-0.2767</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.326499999999999</v>
+        <v>-6.3641</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.72</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.422</v>
+        <v>-0.2861</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.706</v>
+        <v>-6.5803</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.18</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4089</v>
+        <v>0.461</v>
       </c>
       <c r="J252" t="n">
-        <v>10.6314</v>
+        <v>11.986</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2676</v>
+        <v>-0.1814</v>
       </c>
       <c r="J253" t="n">
-        <v>-6.9576</v>
+        <v>-4.7164</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2676</v>
+        <v>-0.1814</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.9576</v>
+        <v>-4.7164</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3207</v>
+        <v>-0.2111</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.338200000000001</v>
+        <v>-5.4886</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.59</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.4212</v>
       </c>
       <c r="J256" t="n">
-        <v>-16.4476</v>
+        <v>-10.9512</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.43</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0435</v>
+        <v>1.0355</v>
       </c>
       <c r="J257" t="n">
-        <v>27.131</v>
+        <v>26.923</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0007</v>
+        <v>1.005</v>
       </c>
       <c r="J258" t="n">
-        <v>26.0182</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.32</v>
       </c>
       <c r="I259" t="n">
-        <v>0.7967</v>
+        <v>0.8217</v>
       </c>
       <c r="J259" t="n">
-        <v>20.7142</v>
+        <v>21.3642</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.15</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3414</v>
+        <v>0.4217</v>
       </c>
       <c r="J260" t="n">
-        <v>8.8764</v>
+        <v>10.9642</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0241</v>
+        <v>0.1022</v>
       </c>
       <c r="J261" t="n">
-        <v>0.6266</v>
+        <v>2.6572</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.55</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2386</v>
+        <v>1.1684</v>
       </c>
       <c r="J262" t="n">
-        <v>27.2492</v>
+        <v>25.7048</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.49</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1166</v>
+        <v>1.0955</v>
       </c>
       <c r="J263" t="n">
-        <v>24.5652</v>
+        <v>24.101</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.43</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.0178</v>
       </c>
       <c r="J264" t="n">
-        <v>21.7228</v>
+        <v>22.3916</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.22</v>
       </c>
       <c r="I265" t="n">
-        <v>0.4737</v>
+        <v>0.5745</v>
       </c>
       <c r="J265" t="n">
-        <v>10.4214</v>
+        <v>12.639</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.18</v>
       </c>
       <c r="I266" t="n">
-        <v>0.3769</v>
+        <v>0.4757</v>
       </c>
       <c r="J266" t="n">
-        <v>8.2918</v>
+        <v>10.4654</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.05</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2716</v>
+        <v>0.2807</v>
       </c>
       <c r="J267" t="n">
-        <v>5.9752</v>
+        <v>6.1754</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.71</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3744</v>
+        <v>-0.2859</v>
       </c>
       <c r="J268" t="n">
-        <v>-8.236800000000001</v>
+        <v>-6.2898</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4101</v>
+        <v>-0.3044</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.0222</v>
+        <v>-6.6968</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.54</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6528</v>
+        <v>-0.442</v>
       </c>
       <c r="J270" t="n">
-        <v>-14.3616</v>
+        <v>-9.724</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.41</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8213</v>
+        <v>-0.5639</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.0686</v>
+        <v>-12.4058</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.37</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9676</v>
       </c>
       <c r="J272" t="n">
-        <v>29.409</v>
+        <v>29.028</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.31</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8467</v>
+        <v>0.8343</v>
       </c>
       <c r="J273" t="n">
-        <v>25.401</v>
+        <v>25.029</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4336</v>
+        <v>0.4464</v>
       </c>
       <c r="J274" t="n">
-        <v>13.008</v>
+        <v>13.392</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.99</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1598</v>
+        <v>-0.0892</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.794</v>
+        <v>-2.676</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4584</v>
+        <v>-0.3891</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.752</v>
+        <v>-11.673</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.55</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8232</v>
+        <v>1.019</v>
       </c>
       <c r="J277" t="n">
-        <v>24.696</v>
+        <v>30.57</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3273</v>
+        <v>0.3664</v>
       </c>
       <c r="J278" t="n">
-        <v>9.819000000000001</v>
+        <v>10.992</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4243</v>
+        <v>-0.2678</v>
       </c>
       <c r="J279" t="n">
-        <v>-12.729</v>
+        <v>-8.034000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.77</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4243</v>
+        <v>-0.2678</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.729</v>
+        <v>-8.034000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.71</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5057</v>
+        <v>-0.3258</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.171</v>
+        <v>-9.773999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3061/event_3061_evp_summary.xlsx
+++ b/database/event/3061/event_3061_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.8194</v>
+        <v>8.913</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3265</v>
+        <v>2.3512</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3435</v>
+        <v>3.4332</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8194</v>
+        <v>8.913</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8957</v>
+        <v>3.8521</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9236</v>
+        <v>5.0608</v>
       </c>
       <c r="H2" t="n">
-        <v>8.239800000000001</v>
+        <v>7.8155</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2843</v>
+        <v>4.2203</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9236</v>
+        <v>5.0608</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>201</v>
       </c>
       <c r="M2" t="n">
-        <v>9.2079</v>
+        <v>9.2811</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9828</v>
+        <v>7.0907</v>
       </c>
       <c r="C3" t="n">
-        <v>1.842</v>
+        <v>1.8705</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5144</v>
+        <v>2.6036</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9828</v>
+        <v>7.0907</v>
       </c>
       <c r="F3" t="n">
-        <v>3.222</v>
+        <v>3.1504</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7608</v>
+        <v>3.9403</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8659</v>
+        <v>5.5001</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7608</v>
+        <v>3.9403</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -575,7 +575,7 @@
         <v>201</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8108</v>
+        <v>6.9103</v>
       </c>
       <c r="N3" t="n">
         <v>342</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2913</v>
+        <v>5.2876</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3958</v>
+        <v>1.3948</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7507</v>
+        <v>1.7828</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2913</v>
+        <v>5.2876</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8899</v>
+        <v>2.8097</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4014</v>
+        <v>2.4779</v>
       </c>
       <c r="H4" t="n">
-        <v>4.696</v>
+        <v>4.3762</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4417</v>
+        <v>2.3631</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4014</v>
+        <v>2.4779</v>
       </c>
       <c r="K4" t="n">
         <v>141</v>
@@ -621,7 +621,7 @@
         <v>201</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8431</v>
+        <v>4.841</v>
       </c>
       <c r="N4" t="n">
         <v>342</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2975</v>
+        <v>4.3655</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1337</v>
+        <v>1.1516</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3021</v>
+        <v>1.3631</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2975</v>
+        <v>4.3655</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3907</v>
+        <v>2.336</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9068</v>
+        <v>2.0295</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9372</v>
+        <v>2.813</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5272</v>
+        <v>1.519</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9068</v>
+        <v>2.0295</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -667,7 +667,7 @@
         <v>173</v>
       </c>
       <c r="M5" t="n">
-        <v>3.434</v>
+        <v>3.5485</v>
       </c>
       <c r="N5" t="n">
         <v>278</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7819</v>
+        <v>3.7192</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9976</v>
+        <v>0.9811</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0693</v>
+        <v>1.0689</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7819</v>
+        <v>3.7192</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0183</v>
+        <v>2.9363</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7829</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1481</v>
+        <v>4.7938</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6768</v>
+        <v>2.5886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7829</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -713,7 +713,7 @@
         <v>173</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4404</v>
+        <v>3.3715</v>
       </c>
       <c r="N6" t="n">
         <v>278</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7247</v>
+        <v>3.7167</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9826</v>
+        <v>0.9804</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0435</v>
+        <v>1.0677</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7247</v>
+        <v>3.7167</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0077</v>
+        <v>2.9426</v>
       </c>
       <c r="G7" t="n">
-        <v>0.717</v>
+        <v>0.7741</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1108</v>
+        <v>4.8147</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6574</v>
+        <v>2.5999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.717</v>
+        <v>0.7741</v>
       </c>
       <c r="K7" t="n">
         <v>141</v>
@@ -759,7 +759,7 @@
         <v>201</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3744</v>
+        <v>3.374</v>
       </c>
       <c r="N7" t="n">
         <v>342</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4239</v>
+        <v>3.3098</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9032</v>
+        <v>0.8731</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9077</v>
+        <v>0.8825</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4239</v>
+        <v>3.3098</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4239</v>
+        <v>2.4526</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.8572</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1584</v>
+        <v>3.1977</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1584</v>
+        <v>1.7268</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.8572</v>
       </c>
       <c r="K8" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1584</v>
+        <v>2.584</v>
       </c>
       <c r="N8" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3314</v>
+        <v>3.1127</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8788</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8659</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3314</v>
+        <v>3.1127</v>
       </c>
       <c r="F9" t="n">
-        <v>2.543</v>
+        <v>2.5511</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7884</v>
+        <v>0.5616</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4735</v>
+        <v>3.5227</v>
       </c>
       <c r="I9" t="n">
-        <v>1.806</v>
+        <v>1.9022</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7884</v>
+        <v>0.5616</v>
       </c>
       <c r="K9" t="n">
         <v>118</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5944</v>
+        <v>2.4638</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1539</v>
+        <v>3.0783</v>
       </c>
       <c r="C10" t="n">
-        <v>0.832</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7771</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1539</v>
+        <v>3.0783</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6431</v>
+        <v>3.0783</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5108</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8264</v>
+        <v>4.0125</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9896</v>
+        <v>4.0125</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5108</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="L10" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5004</v>
+        <v>4.0125</v>
       </c>
       <c r="N10" t="n">
-        <v>200</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1008</v>
+        <v>2.9959</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7903</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7618</v>
+        <v>0.7396</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1008</v>
+        <v>2.9959</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5992</v>
+        <v>2.4917</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5016</v>
+        <v>0.5042</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6715</v>
+        <v>3.3269</v>
       </c>
       <c r="I11" t="n">
-        <v>1.909</v>
+        <v>1.7965</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5016</v>
+        <v>0.5042</v>
       </c>
       <c r="K11" t="n">
         <v>105</v>
@@ -943,7 +943,7 @@
         <v>173</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4106</v>
+        <v>2.3007</v>
       </c>
       <c r="N11" t="n">
         <v>278</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9838</v>
+        <v>2.8785</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7871</v>
+        <v>0.7593</v>
       </c>
       <c r="D12" t="n">
-        <v>0.709</v>
+        <v>0.6861</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9838</v>
+        <v>2.8785</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1959</v>
+        <v>1.053</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7879</v>
+        <v>1.8255</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1959</v>
+        <v>1.053</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6218</v>
+        <v>0.5686</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7879</v>
+        <v>1.8255</v>
       </c>
       <c r="K12" t="n">
         <v>105</v>
@@ -989,7 +989,7 @@
         <v>173</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4097</v>
+        <v>2.3941</v>
       </c>
       <c r="N12" t="n">
         <v>278</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9306</v>
+        <v>2.8753</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7731</v>
+        <v>0.7585</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6847</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9306</v>
+        <v>2.8753</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6674</v>
+        <v>2.5788</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2632</v>
+        <v>0.2965</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9121</v>
+        <v>3.6141</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0341</v>
+        <v>1.9516</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2632</v>
+        <v>0.2965</v>
       </c>
       <c r="K13" t="n">
         <v>132</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2973</v>
+        <v>2.2481</v>
       </c>
       <c r="N13" t="n">
         <v>186</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8242</v>
+        <v>2.8104</v>
       </c>
       <c r="C14" t="n">
-        <v>0.745</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.637</v>
+        <v>0.6551</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8242</v>
+        <v>2.8104</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5714</v>
+        <v>2.526</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2528</v>
+        <v>0.2844</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5737</v>
+        <v>3.4401</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8581</v>
+        <v>1.8576</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2528</v>
+        <v>0.2844</v>
       </c>
       <c r="K14" t="n">
         <v>132</v>
@@ -1081,7 +1081,7 @@
         <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1109</v>
+        <v>2.142</v>
       </c>
       <c r="N14" t="n">
         <v>186</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4102</v>
+        <v>2.3499</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6358</v>
+        <v>0.6199</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4501</v>
+        <v>0.4455</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4102</v>
+        <v>2.3499</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4102</v>
+        <v>1.437</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.9129</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4102</v>
+        <v>1.437</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4102</v>
+        <v>0.776</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.9129</v>
       </c>
       <c r="K15" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4102</v>
+        <v>1.6889</v>
       </c>
       <c r="N15" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3415</v>
+        <v>2.3166</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6177</v>
+        <v>0.6111</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4191</v>
+        <v>0.4304</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3415</v>
+        <v>2.3166</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5069</v>
+        <v>2.3166</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8346</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5069</v>
+        <v>2.3453</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7835</v>
+        <v>2.3453</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8346</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6181</v>
+        <v>2.3453</v>
       </c>
       <c r="N16" t="n">
-        <v>186</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3333</v>
+        <v>2.2419</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6155</v>
+        <v>0.5914</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4154</v>
+        <v>0.3964</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3333</v>
+        <v>2.2419</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6702</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3369</v>
+        <v>-0.3581</v>
       </c>
       <c r="H17" t="n">
-        <v>3.922</v>
+        <v>3.684</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0392</v>
+        <v>1.9894</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3369</v>
+        <v>-0.3581</v>
       </c>
       <c r="K17" t="n">
         <v>132</v>
@@ -1219,7 +1219,7 @@
         <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7023</v>
+        <v>1.6313</v>
       </c>
       <c r="N17" t="n">
         <v>186</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2769</v>
+        <v>2.1929</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6006</v>
+        <v>0.5785</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3899</v>
+        <v>0.374</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2769</v>
+        <v>2.1929</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3613</v>
+        <v>2.2755</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0844</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8335</v>
+        <v>2.6136</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4733</v>
+        <v>1.4113</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0844</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>118</v>
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3889</v>
+        <v>1.3287</v>
       </c>
       <c r="N18" t="n">
         <v>200</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0421</v>
+        <v>1.9605</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5387</v>
+        <v>0.5172</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2839</v>
+        <v>0.2683</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0421</v>
+        <v>1.9605</v>
       </c>
       <c r="F19" t="n">
-        <v>2.218</v>
+        <v>2.1511</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1759</v>
+        <v>-0.1906</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3285</v>
+        <v>2.2031</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2107</v>
+        <v>1.1896</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1759</v>
+        <v>-0.1906</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>82</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0348</v>
+        <v>0.999</v>
       </c>
       <c r="N19" t="n">
         <v>200</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9443</v>
+        <v>1.887</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5129</v>
+        <v>0.4978</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2397</v>
+        <v>0.2348</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9443</v>
+        <v>1.887</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2249</v>
+        <v>2.1419</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2806</v>
+        <v>-0.2549</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3527</v>
+        <v>2.1727</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2233</v>
+        <v>1.1732</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2806</v>
+        <v>-0.2549</v>
       </c>
       <c r="K20" t="n">
         <v>118</v>
@@ -1357,7 +1357,7 @@
         <v>82</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9427000000000001</v>
+        <v>0.9183</v>
       </c>
       <c r="N20" t="n">
         <v>200</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5442</v>
+        <v>1.4043</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4074</v>
+        <v>0.3704</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0591</v>
+        <v>0.0151</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5442</v>
+        <v>1.4043</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1656</v>
+        <v>1.4043</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6214</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1656</v>
+        <v>1.4043</v>
       </c>
       <c r="I21" t="n">
-        <v>1.126</v>
+        <v>1.4043</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6214</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5045999999999999</v>
+        <v>1.4043</v>
       </c>
       <c r="N21" t="n">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4213</v>
+        <v>1.3085</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3749</v>
+        <v>0.3452</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0036</v>
+        <v>-0.0285</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4213</v>
+        <v>1.3085</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4213</v>
+        <v>1.9548</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.6463</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4213</v>
+        <v>1.9548</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4213</v>
+        <v>1.0556</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.6463</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4213</v>
+        <v>0.4093000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>111</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2526</v>
+        <v>1.1961</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3304</v>
+        <v>0.3155</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0725</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2526</v>
+        <v>1.1961</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2526</v>
+        <v>1.1961</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2526</v>
+        <v>1.1961</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2526</v>
+        <v>1.1961</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2526</v>
+        <v>1.1961</v>
       </c>
       <c r="N23" t="n">
         <v>111</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0849</v>
+        <v>1.0486</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2862</v>
+        <v>0.2766</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1482</v>
+        <v>-0.1469</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0849</v>
+        <v>1.0486</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0849</v>
+        <v>1.0486</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0849</v>
+        <v>1.0486</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0849</v>
+        <v>1.0486</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0849</v>
+        <v>1.0486</v>
       </c>
       <c r="N24" t="n">
         <v>111</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9566</v>
+        <v>0.9055</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2523</v>
+        <v>0.2389</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2062</v>
+        <v>-0.212</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9566</v>
+        <v>0.9055</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9566</v>
+        <v>0.9055</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9566</v>
+        <v>0.9055</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9566</v>
+        <v>0.9055</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9566</v>
+        <v>0.9055</v>
       </c>
       <c r="N25" t="n">
         <v>91</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4253</v>
+        <v>0.4049</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1122</v>
+        <v>0.1068</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.446</v>
+        <v>-0.4399</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4253</v>
+        <v>0.4049</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4253</v>
+        <v>0.4049</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4253</v>
+        <v>0.4049</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4253</v>
+        <v>0.4049</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4253</v>
+        <v>0.4049</v>
       </c>
       <c r="N26" t="n">
         <v>111</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3281</v>
+        <v>0.2723</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0866</v>
+        <v>0.0718</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4899</v>
+        <v>-0.5002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3281</v>
+        <v>0.2723</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3281</v>
+        <v>0.2723</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3281</v>
+        <v>0.2723</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3281</v>
+        <v>0.2723</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3281</v>
+        <v>0.2723</v>
       </c>
       <c r="N27" t="n">
         <v>70</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1312</v>
+        <v>0.0868</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0346</v>
+        <v>0.0229</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5788</v>
+        <v>-0.5847</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1312</v>
+        <v>0.0868</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1312</v>
+        <v>0.0868</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1312</v>
+        <v>0.0868</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1312</v>
+        <v>0.0868</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1312</v>
+        <v>0.0868</v>
       </c>
       <c r="N28" t="n">
         <v>91</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0804</v>
+        <v>0.0535</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0212</v>
+        <v>0.0141</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6017</v>
+        <v>-0.5998</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0804</v>
+        <v>0.0535</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0804</v>
+        <v>0.0535</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0804</v>
+        <v>0.0535</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0804</v>
+        <v>0.0535</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0804</v>
+        <v>0.0535</v>
       </c>
       <c r="N29" t="n">
         <v>148</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0246</v>
+        <v>-0.0072</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0065</v>
+        <v>-0.0019</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6269</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0246</v>
+        <v>-0.0072</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0246</v>
+        <v>-0.0072</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0246</v>
+        <v>-0.0072</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0246</v>
+        <v>-0.0072</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0246</v>
+        <v>-0.0072</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1884</v>
+        <v>-0.2627</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0497</v>
+        <v>-0.0693</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7231</v>
+        <v>-0.7438</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1884</v>
+        <v>-0.2627</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1884</v>
+        <v>-0.2627</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1884</v>
+        <v>-0.2627</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1884</v>
+        <v>-0.2627</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1884</v>
+        <v>-0.2627</v>
       </c>
       <c r="N31" t="n">
         <v>148</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2416</v>
+        <v>-0.2853</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7471</v>
+        <v>-0.7541</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2416</v>
+        <v>-0.2853</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2416</v>
+        <v>-0.2853</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2416</v>
+        <v>-0.2853</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2416</v>
+        <v>-0.2853</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2416</v>
+        <v>-0.2853</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3773</v>
+        <v>-0.3281</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0866</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8083</v>
+        <v>-0.7736</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3773</v>
+        <v>-0.3281</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3773</v>
+        <v>-0.3281</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3773</v>
+        <v>-0.3281</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3773</v>
+        <v>-0.3281</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3773</v>
+        <v>-0.3281</v>
       </c>
       <c r="N33" t="n">
         <v>111</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6732</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1706</v>
+        <v>-0.1776</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9301</v>
+        <v>-0.9307</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6732</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6732</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6732</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6732</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6732</v>
       </c>
       <c r="N34" t="n">
         <v>91</v>
@@ -2010,78 +2010,78 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7035</v>
+        <v>-0.7413</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1856</v>
+        <v>-0.1956</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9556</v>
+        <v>-0.9617</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7035</v>
+        <v>-0.7413</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7035</v>
+        <v>-2.0213</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7035</v>
+        <v>-2.0213</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7035</v>
+        <v>-1.0915</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7035</v>
+        <v>0.1885000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9369</v>
+        <v>-0.7548</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2471</v>
+        <v>-0.1991</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.061</v>
+        <v>-0.9678</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9369</v>
+        <v>-0.7548</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9369</v>
+        <v>-0.7548</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9369</v>
+        <v>-0.7548</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9369</v>
+        <v>-0.7548</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9369</v>
+        <v>-0.7548</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -2102,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1028</v>
+        <v>-0.9873</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2909</v>
+        <v>-0.2604</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1359</v>
+        <v>-1.0736</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1028</v>
+        <v>-0.9873</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.2823</v>
+        <v>-0.9873</v>
       </c>
       <c r="G37" t="n">
-        <v>1.1795</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.2823</v>
+        <v>-0.9873</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1867</v>
+        <v>-0.9873</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1795</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="L37" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.007200000000000095</v>
+        <v>-0.9873</v>
       </c>
       <c r="N37" t="n">
-        <v>342</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.145</v>
+        <v>-1.1633</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.302</v>
+        <v>-0.3069</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1549</v>
+        <v>-1.1538</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.145</v>
+        <v>-1.1633</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.145</v>
+        <v>-1.1633</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.145</v>
+        <v>-1.1633</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.145</v>
+        <v>-1.1633</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.145</v>
+        <v>-1.1633</v>
       </c>
       <c r="N38" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.213</v>
+        <v>-1.184</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.32</v>
+        <v>-0.3123</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1856</v>
+        <v>-1.1632</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.213</v>
+        <v>-1.184</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.213</v>
+        <v>-1.184</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.213</v>
+        <v>-1.184</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.213</v>
+        <v>-1.184</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.213</v>
+        <v>-1.184</v>
       </c>
       <c r="N39" t="n">
-        <v>148</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2454</v>
+        <v>-1.2817</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3285</v>
+        <v>-0.3381</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2003</v>
+        <v>-1.2077</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2454</v>
+        <v>-1.2817</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2454</v>
+        <v>-1.2817</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2454</v>
+        <v>-1.2817</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2454</v>
+        <v>-1.2817</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2454</v>
+        <v>-1.2817</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2992</v>
+        <v>-2.2096</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6065</v>
+        <v>-0.5829</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.676</v>
+        <v>-1.6301</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2992</v>
+        <v>-2.2096</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.5897</v>
+        <v>-0.4737</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.7095</v>
+        <v>-1.7359</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5897</v>
+        <v>-0.4737</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3066</v>
+        <v>-0.2558</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.7095</v>
+        <v>-1.7359</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>173</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0161</v>
+        <v>-1.9917</v>
       </c>
       <c r="N41" t="n">
         <v>278</v>
@@ -2429,10 +2429,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1.251</v>
+        <v>1.3082</v>
       </c>
       <c r="J2" t="n">
-        <v>30.024</v>
+        <v>31.3968</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1429</v>
+        <v>1.1513</v>
       </c>
       <c r="J3" t="n">
-        <v>27.4296</v>
+        <v>27.6312</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.931</v>
+        <v>0.8821</v>
       </c>
       <c r="J4" t="n">
-        <v>22.344</v>
+        <v>21.1704</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8041</v>
+        <v>0.7691</v>
       </c>
       <c r="J5" t="n">
-        <v>19.2984</v>
+        <v>18.4584</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1417</v>
+        <v>0.17</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4008</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.17</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4833</v>
+        <v>0.4558</v>
       </c>
       <c r="J7" t="n">
-        <v>11.5992</v>
+        <v>10.9392</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.86</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1518</v>
+        <v>-0.1712</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.6432</v>
+        <v>-4.1088</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2601</v>
+        <v>-0.2791</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.2424</v>
+        <v>-6.6984</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.57</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4295</v>
+        <v>-0.442</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.308</v>
+        <v>-10.608</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4574</v>
+        <v>-0.4683</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.9776</v>
+        <v>-11.2392</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1852</v>
+        <v>-0.2108</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8892</v>
+        <v>-4.4268</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2384</v>
+        <v>-0.2624</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.0064</v>
+        <v>-5.5104</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4073</v>
+        <v>-0.4246</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.5533</v>
+        <v>-8.916600000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4259</v>
+        <v>-0.4422</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.943899999999999</v>
+        <v>-9.286199999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.54</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4353</v>
+        <v>-0.451</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.141299999999999</v>
+        <v>-9.471</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9419</v>
+        <v>0.9285</v>
       </c>
       <c r="J17" t="n">
-        <v>19.7799</v>
+        <v>19.4985</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.76</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8465</v>
+        <v>0.8389</v>
       </c>
       <c r="J18" t="n">
-        <v>17.7765</v>
+        <v>17.6169</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.43</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5162</v>
+        <v>0.5301</v>
       </c>
       <c r="J19" t="n">
-        <v>10.8402</v>
+        <v>11.1321</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2562</v>
+        <v>0.2799</v>
       </c>
       <c r="J20" t="n">
-        <v>5.3802</v>
+        <v>5.8779</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0405</v>
+        <v>-0.0315</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8505</v>
+        <v>-0.6615</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0237</v>
+        <v>0.9683</v>
       </c>
       <c r="J22" t="n">
-        <v>25.5925</v>
+        <v>24.2075</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4481</v>
+        <v>0.441</v>
       </c>
       <c r="J23" t="n">
-        <v>11.2025</v>
+        <v>11.025</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.13</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3975</v>
+        <v>0.3945</v>
       </c>
       <c r="J24" t="n">
-        <v>9.9375</v>
+        <v>9.862500000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3715</v>
+        <v>0.3705</v>
       </c>
       <c r="J25" t="n">
-        <v>9.2875</v>
+        <v>9.262499999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4715</v>
+        <v>-0.4458</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.7875</v>
+        <v>-11.145</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.02</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>2.04</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>2.04</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0523</v>
+        <v>0.0538</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3075</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2304</v>
+        <v>-0.2457</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.76</v>
+        <v>-6.1425</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2403</v>
+        <v>-0.2555</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.0075</v>
+        <v>-6.3875</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.45</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="J32" t="n">
-        <v>19.0472</v>
+        <v>18.5397</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1361</v>
+        <v>0.1469</v>
       </c>
       <c r="J33" t="n">
-        <v>3.9469</v>
+        <v>4.2601</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0527</v>
+        <v>-0.0602</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.5283</v>
+        <v>-1.7458</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.103</v>
+        <v>-0.1138</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.987</v>
+        <v>-3.3002</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3203</v>
+        <v>-0.3316</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.2887</v>
+        <v>-9.616400000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5556</v>
+        <v>0.5599</v>
       </c>
       <c r="J37" t="n">
-        <v>16.1124</v>
+        <v>16.2371</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2363</v>
+        <v>0.2533</v>
       </c>
       <c r="J38" t="n">
-        <v>6.8527</v>
+        <v>7.3457</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.224</v>
+        <v>0.241</v>
       </c>
       <c r="J39" t="n">
-        <v>6.496</v>
+        <v>6.989</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2113</v>
+        <v>0.2283</v>
       </c>
       <c r="J40" t="n">
-        <v>6.1277</v>
+        <v>6.6207</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1618</v>
+        <v>-0.1711</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.6922</v>
+        <v>-4.9619</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.38</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J42" t="n">
-        <v>37.362</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>1.049</v>
+        <v>1.0172</v>
       </c>
       <c r="J43" t="n">
-        <v>20.98</v>
+        <v>20.344</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9175</v>
+        <v>0.8724</v>
       </c>
       <c r="J44" t="n">
-        <v>18.35</v>
+        <v>17.448</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3513</v>
+        <v>0.3683</v>
       </c>
       <c r="J45" t="n">
-        <v>7.026</v>
+        <v>7.366</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1095</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.19</v>
+        <v>-1.526</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.176</v>
+        <v>-0.2015</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.52</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.187</v>
+        <v>-0.2121</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.74</v>
+        <v>-4.242</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.64</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3445</v>
+        <v>-0.3646</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.89</v>
+        <v>-7.292</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.59</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3898</v>
+        <v>-0.4079</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.796</v>
+        <v>-8.157999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.4</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5682</v>
+        <v>-0.5748</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.364</v>
+        <v>-11.496</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.03</v>
       </c>
       <c r="I52" t="n">
-        <v>0.128</v>
+        <v>0.1262</v>
       </c>
       <c r="J52" t="n">
-        <v>3.2</v>
+        <v>3.155</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1427</v>
+        <v>-0.159</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.5675</v>
+        <v>-3.975</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1529</v>
+        <v>-0.1695</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.8225</v>
+        <v>-4.2375</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1928</v>
+        <v>-0.2099</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.82</v>
+        <v>-5.2475</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3006</v>
+        <v>-0.3161</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.515</v>
+        <v>-7.9025</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0928</v>
+        <v>1.0531</v>
       </c>
       <c r="J57" t="n">
-        <v>27.32</v>
+        <v>26.3275</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6239</v>
+        <v>0.6041</v>
       </c>
       <c r="J58" t="n">
-        <v>15.5975</v>
+        <v>15.1025</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6005</v>
+        <v>0.5831</v>
       </c>
       <c r="J59" t="n">
-        <v>15.0125</v>
+        <v>14.5775</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.17</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4784</v>
+        <v>0.4732</v>
       </c>
       <c r="J60" t="n">
-        <v>11.96</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.14</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4009</v>
+        <v>0.4029</v>
       </c>
       <c r="J61" t="n">
-        <v>10.0225</v>
+        <v>10.0725</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.67</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7896</v>
+        <v>0.7813</v>
       </c>
       <c r="J62" t="n">
-        <v>18.1608</v>
+        <v>17.9699</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5018</v>
+        <v>0.5129</v>
       </c>
       <c r="J63" t="n">
-        <v>11.5414</v>
+        <v>11.7967</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.35</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4466</v>
+        <v>0.4605</v>
       </c>
       <c r="J64" t="n">
-        <v>10.2718</v>
+        <v>10.5915</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0464</v>
+        <v>-0.0453</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.0672</v>
+        <v>-1.0419</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1153</v>
+        <v>-0.1202</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.6519</v>
+        <v>-2.7646</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.15</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2976</v>
+        <v>0.2964</v>
       </c>
       <c r="J67" t="n">
-        <v>6.8448</v>
+        <v>6.8172</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1333</v>
+        <v>-0.149</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.0659</v>
+        <v>-3.427</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.1543</v>
+        <v>-5.5384</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2439</v>
+        <v>-0.2604</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.6097</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2537</v>
+        <v>-0.27</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.8351</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.04</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1883</v>
+        <v>0.1774</v>
       </c>
       <c r="J72" t="n">
-        <v>4.1426</v>
+        <v>3.9028</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0969</v>
+        <v>-0.1153</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.1318</v>
+        <v>-2.5366</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2144</v>
+        <v>-0.2334</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.7168</v>
+        <v>-5.1348</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3085</v>
+        <v>-0.326</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.787</v>
+        <v>-7.172</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.48</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.514</v>
+        <v>-0.5214</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.308</v>
+        <v>-11.4708</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5276</v>
+        <v>1.5207</v>
       </c>
       <c r="J77" t="n">
-        <v>33.6072</v>
+        <v>33.4554</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.35</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8731</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>19.2082</v>
+        <v>18.2402</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.35</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8731</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>19.2082</v>
+        <v>18.2402</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8519</v>
+        <v>0.8104</v>
       </c>
       <c r="J80" t="n">
-        <v>18.7418</v>
+        <v>17.8288</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4678</v>
+        <v>-0.4316</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.2916</v>
+        <v>-9.495200000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6324</v>
+        <v>0.7024</v>
       </c>
       <c r="J82" t="n">
-        <v>17.7072</v>
+        <v>19.6672</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.3216</v>
+        <v>-1.5708</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1833</v>
+        <v>-0.1979</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.1324</v>
+        <v>-5.5412</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1833</v>
+        <v>-0.1979</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.1324</v>
+        <v>-5.5412</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3221</v>
+        <v>-0.3348</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.018800000000001</v>
+        <v>-9.3744</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.45</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8114</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>22.7192</v>
+        <v>25.0516</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.26</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5553</v>
+        <v>0.615</v>
       </c>
       <c r="J88" t="n">
-        <v>15.5484</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.14</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3835</v>
+        <v>0.414</v>
       </c>
       <c r="J89" t="n">
-        <v>10.738</v>
+        <v>11.592</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.6572</v>
+        <v>-2.4472</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.6572</v>
+        <v>-2.4472</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.25</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4465</v>
+        <v>0.4944</v>
       </c>
       <c r="J92" t="n">
-        <v>11.609</v>
+        <v>12.8544</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4361</v>
+        <v>0.4823</v>
       </c>
       <c r="J93" t="n">
-        <v>11.3386</v>
+        <v>12.5398</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2022</v>
+        <v>0.2105</v>
       </c>
       <c r="J94" t="n">
-        <v>5.2572</v>
+        <v>5.473</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2897</v>
+        <v>-0.302</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.5322</v>
+        <v>-7.852</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.74</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2993</v>
+        <v>-0.3115</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.7818</v>
+        <v>-8.099</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6498</v>
+        <v>0.7136</v>
       </c>
       <c r="J97" t="n">
-        <v>16.8948</v>
+        <v>18.5536</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.13</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3815</v>
+        <v>0.4058</v>
       </c>
       <c r="J98" t="n">
-        <v>9.919</v>
+        <v>10.5508</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3654</v>
+        <v>0.3812</v>
       </c>
       <c r="J99" t="n">
-        <v>9.500400000000001</v>
+        <v>9.911199999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3489</v>
+        <v>0.3559</v>
       </c>
       <c r="J100" t="n">
-        <v>9.071400000000001</v>
+        <v>9.253399999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.61</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.1062</v>
+        <v>-1.0073</v>
       </c>
       <c r="J101" t="n">
-        <v>-28.7612</v>
+        <v>-26.1898</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.43</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4677</v>
+        <v>0.5313</v>
       </c>
       <c r="J102" t="n">
-        <v>14.031</v>
+        <v>15.939</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.26</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3506</v>
+        <v>0.3757</v>
       </c>
       <c r="J103" t="n">
-        <v>10.518</v>
+        <v>11.271</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2129</v>
+        <v>0.2294</v>
       </c>
       <c r="J104" t="n">
-        <v>6.387</v>
+        <v>6.882</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0853</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>2.559</v>
+        <v>2.985</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2827</v>
+        <v>-0.2927</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.481</v>
+        <v>-8.781000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4241</v>
+        <v>0.4718</v>
       </c>
       <c r="J107" t="n">
-        <v>12.723</v>
+        <v>14.154</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4087</v>
+        <v>0.453</v>
       </c>
       <c r="J108" t="n">
-        <v>12.261</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1013</v>
+        <v>0.1119</v>
       </c>
       <c r="J109" t="n">
-        <v>3.039</v>
+        <v>3.357</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0466</v>
+        <v>0.0547</v>
       </c>
       <c r="J110" t="n">
-        <v>1.398</v>
+        <v>1.641</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.52</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5053</v>
+        <v>-0.509</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.159</v>
+        <v>-15.27</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3115</v>
+        <v>0.3051</v>
       </c>
       <c r="J112" t="n">
-        <v>6.853</v>
+        <v>6.7122</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1535</v>
+        <v>0.1518</v>
       </c>
       <c r="J113" t="n">
-        <v>3.377</v>
+        <v>3.3396</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.85</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1728</v>
+        <v>-0.1898</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.8016</v>
+        <v>-4.1756</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2619</v>
+        <v>-0.2784</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.7618</v>
+        <v>-6.1248</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.57</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4415</v>
+        <v>-0.4514</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.712999999999999</v>
+        <v>-9.9308</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.76</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1534</v>
+        <v>1.2669</v>
       </c>
       <c r="J117" t="n">
-        <v>25.3748</v>
+        <v>27.8718</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6904</v>
+        <v>0.7698</v>
       </c>
       <c r="J118" t="n">
-        <v>15.1888</v>
+        <v>16.9356</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4662</v>
+        <v>0.5203</v>
       </c>
       <c r="J119" t="n">
-        <v>10.2564</v>
+        <v>11.4466</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4074</v>
+        <v>0.4532</v>
       </c>
       <c r="J120" t="n">
-        <v>8.9628</v>
+        <v>9.9704</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.16</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3923</v>
+        <v>0.4338</v>
       </c>
       <c r="J121" t="n">
-        <v>8.630599999999999</v>
+        <v>9.5436</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4436</v>
+        <v>0.4892</v>
       </c>
       <c r="J122" t="n">
-        <v>13.308</v>
+        <v>14.676</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4221</v>
+        <v>0.4643</v>
       </c>
       <c r="J123" t="n">
-        <v>12.663</v>
+        <v>13.929</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1672</v>
+        <v>0.1741</v>
       </c>
       <c r="J124" t="n">
-        <v>5.016</v>
+        <v>5.223</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.216</v>
+        <v>-0.2302</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.48</v>
+        <v>-6.906</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4812</v>
+        <v>-0.4872</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.436</v>
+        <v>-14.616</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.69</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1251</v>
+        <v>1.2275</v>
       </c>
       <c r="J127" t="n">
-        <v>33.753</v>
+        <v>36.825</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5309</v>
+        <v>0.587</v>
       </c>
       <c r="J128" t="n">
-        <v>15.927</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5024</v>
+        <v>0.5551</v>
       </c>
       <c r="J129" t="n">
-        <v>15.072</v>
+        <v>16.653</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.87</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4741</v>
+        <v>-0.4477</v>
       </c>
       <c r="J130" t="n">
-        <v>-14.223</v>
+        <v>-13.431</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.8359</v>
       </c>
       <c r="J131" t="n">
-        <v>-27.354</v>
+        <v>-25.077</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.67</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3013</v>
+        <v>1.2843</v>
       </c>
       <c r="J132" t="n">
-        <v>26.026</v>
+        <v>25.686</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>1.124</v>
+        <v>1.0939</v>
       </c>
       <c r="J133" t="n">
-        <v>22.48</v>
+        <v>21.878</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.45</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0391</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>20.782</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.37</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9036</v>
+        <v>0.8585</v>
       </c>
       <c r="J135" t="n">
-        <v>18.072</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.15</v>
       </c>
       <c r="I136" t="n">
-        <v>0.386</v>
+        <v>0.3981</v>
       </c>
       <c r="J136" t="n">
-        <v>7.72</v>
+        <v>7.962</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0582</v>
+        <v>-0.0876</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.164</v>
+        <v>-1.752</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.68</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3027</v>
+        <v>-0.3253</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.054</v>
+        <v>-6.506</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4305</v>
+        <v>-0.4473</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.946</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.5</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.468</v>
+        <v>-0.4825</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.65</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5058</v>
+        <v>-0.5177</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.116</v>
+        <v>-10.354</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3175</v>
+        <v>1.2834</v>
       </c>
       <c r="J142" t="n">
-        <v>38.2075</v>
+        <v>37.2186</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.154</v>
+        <v>0.1618</v>
       </c>
       <c r="J143" t="n">
-        <v>4.466</v>
+        <v>4.6922</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0837</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>2.4273</v>
+        <v>2.6912</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0112</v>
+        <v>-0.0076</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.3248</v>
+        <v>-0.2204</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.1057</v>
+        <v>-1.007</v>
       </c>
       <c r="J146" t="n">
-        <v>-32.0653</v>
+        <v>-29.203</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8629</v>
+        <v>0.822</v>
       </c>
       <c r="J147" t="n">
-        <v>25.0241</v>
+        <v>23.838</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.09</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2143</v>
+        <v>0.2244</v>
       </c>
       <c r="J148" t="n">
-        <v>6.2147</v>
+        <v>6.5076</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1311</v>
+        <v>0.142</v>
       </c>
       <c r="J149" t="n">
-        <v>3.8019</v>
+        <v>4.118</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.84</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2047</v>
+        <v>-0.2169</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.9363</v>
+        <v>-6.2901</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.84</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2047</v>
+        <v>-0.2169</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.9363</v>
+        <v>-6.2901</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.18</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3783</v>
+        <v>0.3823</v>
       </c>
       <c r="J152" t="n">
-        <v>11.349</v>
+        <v>11.469</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3419</v>
+        <v>0.348</v>
       </c>
       <c r="J153" t="n">
-        <v>10.257</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1902</v>
+        <v>0.2019</v>
       </c>
       <c r="J154" t="n">
-        <v>5.706</v>
+        <v>6.057</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1484</v>
+        <v>0.1607</v>
       </c>
       <c r="J155" t="n">
-        <v>4.452</v>
+        <v>4.821</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.059</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.77</v>
+        <v>-1.953</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.53</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2044</v>
+        <v>1.1671</v>
       </c>
       <c r="J157" t="n">
-        <v>36.132</v>
+        <v>35.013</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4002</v>
+        <v>0.3963</v>
       </c>
       <c r="J158" t="n">
-        <v>12.006</v>
+        <v>11.889</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3741</v>
+        <v>0.3722</v>
       </c>
       <c r="J159" t="n">
-        <v>11.223</v>
+        <v>11.166</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1405</v>
+        <v>0.1526</v>
       </c>
       <c r="J160" t="n">
-        <v>4.215</v>
+        <v>4.578</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7809</v>
+        <v>-0.7227</v>
       </c>
       <c r="J161" t="n">
-        <v>-23.427</v>
+        <v>-21.681</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.05</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1584</v>
+        <v>0.1617</v>
       </c>
       <c r="J162" t="n">
-        <v>4.752</v>
+        <v>4.851</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.02</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0827</v>
+        <v>0.0853</v>
       </c>
       <c r="J163" t="n">
-        <v>2.481</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.86</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1687</v>
+        <v>-0.1841</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.061</v>
+        <v>-5.523</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.86</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1687</v>
+        <v>-0.1841</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.061</v>
+        <v>-5.523</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1996</v>
+        <v>-0.2152</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.988</v>
+        <v>-6.456</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.57</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2096</v>
+        <v>1.181</v>
       </c>
       <c r="J167" t="n">
-        <v>36.288</v>
+        <v>35.43</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.32</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8185</v>
+        <v>0.7789</v>
       </c>
       <c r="J168" t="n">
-        <v>24.555</v>
+        <v>23.367</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7746</v>
+        <v>0.74</v>
       </c>
       <c r="J169" t="n">
-        <v>23.238</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.27</v>
       </c>
       <c r="I170" t="n">
-        <v>0.709</v>
+        <v>0.6815</v>
       </c>
       <c r="J170" t="n">
-        <v>21.27</v>
+        <v>20.445</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2029</v>
+        <v>-0.1862</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.087</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.23</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4203</v>
+        <v>0.4115</v>
       </c>
       <c r="J172" t="n">
-        <v>10.0872</v>
+        <v>9.875999999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2541</v>
+        <v>0.254</v>
       </c>
       <c r="J173" t="n">
-        <v>6.0984</v>
+        <v>6.096</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0537</v>
+        <v>0.0523</v>
       </c>
       <c r="J174" t="n">
-        <v>1.2888</v>
+        <v>1.2552</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4967</v>
+        <v>-0.5036</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.9208</v>
+        <v>-12.0864</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.47</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5331</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.7944</v>
+        <v>-12.9072</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.62</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7252</v>
+        <v>0.7238</v>
       </c>
       <c r="J177" t="n">
-        <v>17.4048</v>
+        <v>17.3712</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5153</v>
+        <v>0.5273</v>
       </c>
       <c r="J178" t="n">
-        <v>12.3672</v>
+        <v>12.6552</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.39</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4832</v>
+        <v>0.4967</v>
       </c>
       <c r="J179" t="n">
-        <v>11.5968</v>
+        <v>11.9208</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.25</v>
       </c>
       <c r="I180" t="n">
-        <v>0.329</v>
+        <v>0.3482</v>
       </c>
       <c r="J180" t="n">
-        <v>7.896</v>
+        <v>8.3568</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0521</v>
+        <v>-0.0497</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.2504</v>
+        <v>-1.1928</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3766</v>
+        <v>1.3612</v>
       </c>
       <c r="J182" t="n">
-        <v>31.6618</v>
+        <v>31.3076</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.68</v>
       </c>
       <c r="I183" t="n">
-        <v>1.329</v>
+        <v>1.3108</v>
       </c>
       <c r="J183" t="n">
-        <v>30.567</v>
+        <v>30.1484</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.17</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4555</v>
+        <v>0.4573</v>
       </c>
       <c r="J184" t="n">
-        <v>10.4765</v>
+        <v>10.5179</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3234</v>
+        <v>0.3373</v>
       </c>
       <c r="J185" t="n">
-        <v>7.4382</v>
+        <v>7.7579</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1487</v>
+        <v>0.175</v>
       </c>
       <c r="J186" t="n">
-        <v>3.4201</v>
+        <v>4.025</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2465</v>
+        <v>0.2322</v>
       </c>
       <c r="J187" t="n">
-        <v>5.6695</v>
+        <v>5.3406</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0304</v>
+        <v>0.0061</v>
       </c>
       <c r="J188" t="n">
-        <v>0.6992</v>
+        <v>0.1403</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.64</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3628</v>
+        <v>-0.3787</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.3444</v>
+        <v>-8.710100000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.63</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3722</v>
+        <v>-0.3877</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.560600000000001</v>
+        <v>-8.9171</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4655</v>
+        <v>-0.4762</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.7065</v>
+        <v>-10.9526</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.64</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3142</v>
+        <v>1.2891</v>
       </c>
       <c r="J192" t="n">
-        <v>28.9124</v>
+        <v>28.3602</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.32</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8354</v>
+        <v>0.7904</v>
       </c>
       <c r="J193" t="n">
-        <v>18.3788</v>
+        <v>17.3888</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.628</v>
+        <v>0.6068</v>
       </c>
       <c r="J194" t="n">
-        <v>13.816</v>
+        <v>13.3496</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.16</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4598</v>
+        <v>0.4549</v>
       </c>
       <c r="J195" t="n">
-        <v>10.1156</v>
+        <v>10.0078</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.879</v>
+        <v>-0.8046</v>
       </c>
       <c r="J196" t="n">
-        <v>-19.338</v>
+        <v>-17.7012</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3229</v>
+        <v>0.3175</v>
       </c>
       <c r="J197" t="n">
-        <v>7.1038</v>
+        <v>6.985</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.078</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.716</v>
+        <v>-2.0086</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1854</v>
+        <v>-0.2019</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.0788</v>
+        <v>-4.4418</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2355</v>
+        <v>-0.2518</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.181</v>
+        <v>-5.5396</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.265</v>
+        <v>-0.2808</v>
       </c>
       <c r="J201" t="n">
-        <v>-5.83</v>
+        <v>-6.1776</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4369</v>
+        <v>0.4139</v>
       </c>
       <c r="J202" t="n">
-        <v>10.0487</v>
+        <v>9.5197</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.9</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1086</v>
+        <v>-0.1272</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.4978</v>
+        <v>-2.9256</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2517</v>
+        <v>-0.2705</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.7891</v>
+        <v>-6.2215</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3463</v>
+        <v>-0.3625</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.9649</v>
+        <v>-8.3375</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.46</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5324</v>
+        <v>-0.5386</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.2452</v>
+        <v>-12.3878</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.83</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4979</v>
+        <v>1.4906</v>
       </c>
       <c r="J207" t="n">
-        <v>34.4517</v>
+        <v>34.2838</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.143</v>
+        <v>1.113</v>
       </c>
       <c r="J208" t="n">
-        <v>26.289</v>
+        <v>25.599</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6911</v>
+        <v>0.6692</v>
       </c>
       <c r="J209" t="n">
-        <v>15.8953</v>
+        <v>15.3916</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.15</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3967</v>
+        <v>0.4056</v>
       </c>
       <c r="J210" t="n">
-        <v>9.1241</v>
+        <v>9.328799999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.13</v>
       </c>
       <c r="I211" t="n">
-        <v>0.3435</v>
+        <v>0.3572</v>
       </c>
       <c r="J211" t="n">
-        <v>7.9005</v>
+        <v>8.2156</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1437</v>
+        <v>0.1377</v>
       </c>
       <c r="J212" t="n">
-        <v>3.4488</v>
+        <v>3.3048</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>0.006</v>
+        <v>-0.0068</v>
       </c>
       <c r="J213" t="n">
-        <v>0.144</v>
+        <v>-0.1632</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0805</v>
+        <v>-0.0965</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.932</v>
+        <v>-2.316</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3991</v>
+        <v>-0.4119</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.5784</v>
+        <v>-9.8856</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.57</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4363</v>
+        <v>-0.4473</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.4712</v>
+        <v>-10.7352</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3666</v>
+        <v>1.3482</v>
       </c>
       <c r="J217" t="n">
-        <v>32.7984</v>
+        <v>32.3568</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.68</v>
       </c>
       <c r="I218" t="n">
-        <v>1.3425</v>
+        <v>1.3227</v>
       </c>
       <c r="J218" t="n">
-        <v>32.22</v>
+        <v>31.7448</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.18</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4936</v>
+        <v>0.4891</v>
       </c>
       <c r="J219" t="n">
-        <v>11.8464</v>
+        <v>11.7384</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2393</v>
+        <v>-0.221</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.7432</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3048</v>
+        <v>-0.2833</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.3152</v>
+        <v>-6.7992</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.09</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2566</v>
+        <v>0.2551</v>
       </c>
       <c r="J222" t="n">
-        <v>7.1848</v>
+        <v>7.1428</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0902</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>2.5256</v>
+        <v>2.5424</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.84</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1863</v>
+        <v>-0.2026</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.2164</v>
+        <v>-5.6728</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.79</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2366</v>
+        <v>-0.2526</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.6248</v>
+        <v>-7.0728</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2758</v>
+        <v>-0.2912</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.7224</v>
+        <v>-8.153600000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.61</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2836</v>
+        <v>1.2554</v>
       </c>
       <c r="J227" t="n">
-        <v>35.9408</v>
+        <v>35.1512</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7033</v>
+        <v>0.6728</v>
       </c>
       <c r="J228" t="n">
-        <v>19.6924</v>
+        <v>18.8384</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3048</v>
+        <v>0.3118</v>
       </c>
       <c r="J229" t="n">
-        <v>8.5344</v>
+        <v>8.730399999999999</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2173</v>
+        <v>0.2303</v>
       </c>
       <c r="J230" t="n">
-        <v>6.0844</v>
+        <v>6.4484</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3717</v>
+        <v>-0.3514</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.4076</v>
+        <v>-9.8392</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.36</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8762</v>
       </c>
       <c r="J232" t="n">
-        <v>31.756</v>
+        <v>29.7908</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.22</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6101</v>
+        <v>0.5896</v>
       </c>
       <c r="J233" t="n">
-        <v>20.7434</v>
+        <v>20.0464</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4403</v>
+        <v>0.4358</v>
       </c>
       <c r="J234" t="n">
-        <v>14.9702</v>
+        <v>14.8172</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.14</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4145</v>
+        <v>0.4122</v>
       </c>
       <c r="J235" t="n">
-        <v>14.093</v>
+        <v>14.0148</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1563</v>
+        <v>0.1722</v>
       </c>
       <c r="J236" t="n">
-        <v>5.3142</v>
+        <v>5.8548</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.2</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4608</v>
+        <v>0.45</v>
       </c>
       <c r="J237" t="n">
-        <v>15.6672</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0109</v>
+        <v>0.0078</v>
       </c>
       <c r="J238" t="n">
-        <v>0.3706</v>
+        <v>0.2652</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.86</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1703</v>
+        <v>-0.1853</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.7902</v>
+        <v>-6.3002</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.191</v>
+        <v>-0.2062</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.494</v>
+        <v>-7.0108</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2416</v>
+        <v>-0.2565</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.214399999999999</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.7</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3511</v>
+        <v>1.3345</v>
       </c>
       <c r="J242" t="n">
-        <v>31.0753</v>
+        <v>30.6935</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.69</v>
       </c>
       <c r="I243" t="n">
-        <v>1.3392</v>
+        <v>1.322</v>
       </c>
       <c r="J243" t="n">
-        <v>30.8016</v>
+        <v>30.406</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.43</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0201</v>
+        <v>0.9725</v>
       </c>
       <c r="J244" t="n">
-        <v>23.4623</v>
+        <v>22.3675</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.402</v>
+        <v>0.4093</v>
       </c>
       <c r="J245" t="n">
-        <v>9.246</v>
+        <v>9.4139</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6576</v>
+        <v>-0.6034</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.1248</v>
+        <v>-13.8782</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.89</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1148</v>
+        <v>-0.1348</v>
       </c>
       <c r="J247" t="n">
-        <v>-2.6404</v>
+        <v>-3.1004</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.73</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2767</v>
+        <v>-0.2958</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.3641</v>
+        <v>-6.8034</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2767</v>
+        <v>-0.2958</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.3641</v>
+        <v>-6.8034</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.73</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2767</v>
+        <v>-0.2958</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.3641</v>
+        <v>-6.8034</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.72</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2861</v>
+        <v>-0.3049</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.5803</v>
+        <v>-7.0127</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.18</v>
       </c>
       <c r="I252" t="n">
-        <v>0.461</v>
+        <v>0.4429</v>
       </c>
       <c r="J252" t="n">
-        <v>11.986</v>
+        <v>11.5154</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1814</v>
+        <v>-0.1989</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.7164</v>
+        <v>-5.1714</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1814</v>
+        <v>-0.1989</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.7164</v>
+        <v>-5.1714</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2111</v>
+        <v>-0.2286</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.4886</v>
+        <v>-5.9436</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.59</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4212</v>
+        <v>-0.4324</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.9512</v>
+        <v>-11.2424</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.43</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0355</v>
+        <v>0.9866</v>
       </c>
       <c r="J257" t="n">
-        <v>26.923</v>
+        <v>25.6516</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>1.005</v>
+        <v>0.9522</v>
       </c>
       <c r="J258" t="n">
-        <v>26.13</v>
+        <v>24.7572</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.32</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8217</v>
+        <v>0.781</v>
       </c>
       <c r="J259" t="n">
-        <v>21.3642</v>
+        <v>20.306</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.15</v>
       </c>
       <c r="I260" t="n">
-        <v>0.4217</v>
+        <v>0.423</v>
       </c>
       <c r="J260" t="n">
-        <v>10.9642</v>
+        <v>10.998</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.1022</v>
+        <v>0.1259</v>
       </c>
       <c r="J261" t="n">
-        <v>2.6572</v>
+        <v>3.2734</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.55</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1684</v>
+        <v>1.1401</v>
       </c>
       <c r="J262" t="n">
-        <v>25.7048</v>
+        <v>25.0822</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.49</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0955</v>
+        <v>1.061</v>
       </c>
       <c r="J263" t="n">
-        <v>24.101</v>
+        <v>23.342</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.43</v>
       </c>
       <c r="I264" t="n">
-        <v>1.0178</v>
+        <v>0.9705</v>
       </c>
       <c r="J264" t="n">
-        <v>22.3916</v>
+        <v>21.351</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.22</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5745</v>
+        <v>0.5652</v>
       </c>
       <c r="J265" t="n">
-        <v>12.639</v>
+        <v>12.4344</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.18</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4757</v>
+        <v>0.4766</v>
       </c>
       <c r="J266" t="n">
-        <v>10.4654</v>
+        <v>10.4852</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.05</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2807</v>
+        <v>0.2519</v>
       </c>
       <c r="J267" t="n">
-        <v>6.1754</v>
+        <v>5.5418</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.71</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2859</v>
+        <v>-0.3068</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.2898</v>
+        <v>-6.7496</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3044</v>
+        <v>-0.3247</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.6968</v>
+        <v>-7.1434</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.54</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.442</v>
+        <v>-0.4562</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.724</v>
+        <v>-10.0364</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.41</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5639</v>
+        <v>-0.57</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.4058</v>
+        <v>-12.54</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.37</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9676</v>
+        <v>0.9061</v>
       </c>
       <c r="J272" t="n">
-        <v>29.028</v>
+        <v>27.183</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.31</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8343</v>
+        <v>0.7855</v>
       </c>
       <c r="J273" t="n">
-        <v>25.029</v>
+        <v>23.565</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4464</v>
+        <v>0.4399</v>
       </c>
       <c r="J274" t="n">
-        <v>13.392</v>
+        <v>13.197</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.99</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0892</v>
+        <v>-0.0834</v>
       </c>
       <c r="J275" t="n">
-        <v>-2.676</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3891</v>
+        <v>-0.37</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.673</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.55</v>
       </c>
       <c r="I277" t="n">
-        <v>1.019</v>
+        <v>0.9704</v>
       </c>
       <c r="J277" t="n">
-        <v>30.57</v>
+        <v>29.112</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3664</v>
+        <v>0.3658</v>
       </c>
       <c r="J278" t="n">
-        <v>10.992</v>
+        <v>10.974</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2678</v>
+        <v>-0.281</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.034000000000001</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.77</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2678</v>
+        <v>-0.281</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.034000000000001</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.71</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3258</v>
+        <v>-0.3377</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.773999999999999</v>
+        <v>-10.131</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3061/event_3061_evp_summary.xlsx
+++ b/database/event/3061/event_3061_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.913</v>
+        <v>8.869400000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3512</v>
+        <v>2.3397</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4332</v>
+        <v>3.4346</v>
       </c>
       <c r="E2" t="n">
-        <v>8.913</v>
+        <v>8.869400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8521</v>
+        <v>3.6938</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0608</v>
+        <v>5.1756</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8155</v>
+        <v>7.4253</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2203</v>
+        <v>4.1691</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0608</v>
+        <v>5.1756</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>201</v>
       </c>
       <c r="M2" t="n">
-        <v>9.2811</v>
+        <v>9.3447</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0907</v>
+        <v>7.162</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8705</v>
+        <v>1.8893</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6036</v>
+        <v>2.6568</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0907</v>
+        <v>7.162</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1504</v>
+        <v>3.1152</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9403</v>
+        <v>4.0468</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5001</v>
+        <v>5.253</v>
       </c>
       <c r="I3" t="n">
-        <v>2.97</v>
+        <v>2.9494</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9403</v>
+        <v>4.0468</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -575,7 +575,7 @@
         <v>201</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9103</v>
+        <v>6.9962</v>
       </c>
       <c r="N3" t="n">
         <v>342</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2876</v>
+        <v>5.2291</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3948</v>
+        <v>1.3794</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7828</v>
+        <v>1.7763</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2876</v>
+        <v>5.2291</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8097</v>
+        <v>2.8365</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4779</v>
+        <v>2.3926</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3762</v>
+        <v>4.2066</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3631</v>
+        <v>2.3619</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4779</v>
+        <v>2.3926</v>
       </c>
       <c r="K4" t="n">
         <v>141</v>
@@ -621,7 +621,7 @@
         <v>201</v>
       </c>
       <c r="M4" t="n">
-        <v>4.841</v>
+        <v>4.7545</v>
       </c>
       <c r="N4" t="n">
         <v>342</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3655</v>
+        <v>4.302</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1516</v>
+        <v>1.1348</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3631</v>
+        <v>1.354</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3655</v>
+        <v>4.302</v>
       </c>
       <c r="F5" t="n">
-        <v>2.336</v>
+        <v>2.4273</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0295</v>
+        <v>1.8747</v>
       </c>
       <c r="H5" t="n">
-        <v>2.813</v>
+        <v>2.6707</v>
       </c>
       <c r="I5" t="n">
-        <v>1.519</v>
+        <v>1.4995</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0295</v>
+        <v>1.8747</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -667,7 +667,7 @@
         <v>173</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5485</v>
+        <v>3.3742</v>
       </c>
       <c r="N5" t="n">
         <v>278</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7192</v>
+        <v>3.6394</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9811</v>
+        <v>0.9601</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0689</v>
+        <v>1.0521</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7192</v>
+        <v>3.6394</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9363</v>
+        <v>2.9231</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7829</v>
+        <v>0.7163</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7938</v>
+        <v>4.532</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5886</v>
+        <v>2.5446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7829</v>
+        <v>0.7163</v>
       </c>
       <c r="K6" t="n">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="L6" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3715</v>
+        <v>3.2609</v>
       </c>
       <c r="N6" t="n">
-        <v>278</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7167</v>
+        <v>3.6189</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9804</v>
+        <v>0.9546</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0677</v>
+        <v>1.0428</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7167</v>
+        <v>3.6189</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9426</v>
+        <v>2.9544</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7741</v>
+        <v>0.6645</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8147</v>
+        <v>4.6494</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5999</v>
+        <v>2.6105</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7741</v>
+        <v>0.6645</v>
       </c>
       <c r="K7" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="L7" t="n">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="M7" t="n">
-        <v>3.374</v>
+        <v>3.275</v>
       </c>
       <c r="N7" t="n">
-        <v>342</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3098</v>
+        <v>3.2567</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8731</v>
+        <v>0.8591</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8825</v>
+        <v>0.8778</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3098</v>
+        <v>3.2567</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4526</v>
+        <v>2.511</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8572</v>
+        <v>0.7457</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1977</v>
+        <v>2.9849</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7268</v>
+        <v>1.6759</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8572</v>
+        <v>0.7457</v>
       </c>
       <c r="K8" t="n">
         <v>118</v>
@@ -805,7 +805,7 @@
         <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.584</v>
+        <v>2.4216</v>
       </c>
       <c r="N8" t="n">
         <v>200</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1127</v>
+        <v>3.075</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8112</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1127</v>
+        <v>3.075</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5511</v>
+        <v>2.6049</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5616</v>
+        <v>0.4701</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5227</v>
+        <v>3.3371</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9022</v>
+        <v>1.8737</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5616</v>
+        <v>0.4701</v>
       </c>
       <c r="K9" t="n">
         <v>118</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4638</v>
+        <v>2.3438</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0783</v>
+        <v>3.0119</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7945</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7771</v>
+        <v>0.7663</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0783</v>
+        <v>3.0119</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0783</v>
+        <v>3.0119</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0125</v>
+        <v>3.9523</v>
       </c>
       <c r="I10" t="n">
-        <v>4.0125</v>
+        <v>3.9523</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0125</v>
+        <v>3.9523</v>
       </c>
       <c r="N10" t="n">
         <v>148</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9959</v>
+        <v>2.9283</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7903</v>
+        <v>0.7725</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7396</v>
+        <v>0.7282</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9959</v>
+        <v>2.9283</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4917</v>
+        <v>2.5615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5042</v>
+        <v>0.3668</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3269</v>
+        <v>3.1744</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7965</v>
+        <v>1.7823</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5042</v>
+        <v>0.3668</v>
       </c>
       <c r="K11" t="n">
         <v>105</v>
@@ -943,7 +943,7 @@
         <v>173</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3007</v>
+        <v>2.1491</v>
       </c>
       <c r="N11" t="n">
         <v>278</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8785</v>
+        <v>2.8897</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7593</v>
+        <v>0.7623</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6861</v>
+        <v>0.7106</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8785</v>
+        <v>2.8897</v>
       </c>
       <c r="F12" t="n">
-        <v>1.053</v>
+        <v>2.6123</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8255</v>
+        <v>0.2774</v>
       </c>
       <c r="H12" t="n">
-        <v>1.053</v>
+        <v>3.3652</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5686</v>
+        <v>1.8894</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8255</v>
+        <v>0.2774</v>
       </c>
       <c r="K12" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L12" t="n">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3941</v>
+        <v>2.1668</v>
       </c>
       <c r="N12" t="n">
-        <v>278</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8753</v>
+        <v>2.8237</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7585</v>
+        <v>0.7449</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6847</v>
+        <v>0.6805</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8753</v>
+        <v>2.8237</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5788</v>
+        <v>2.5625</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2965</v>
+        <v>0.2612</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6141</v>
+        <v>3.178</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9516</v>
+        <v>1.7844</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2965</v>
+        <v>0.2612</v>
       </c>
       <c r="K13" t="n">
         <v>132</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2481</v>
+        <v>2.0456</v>
       </c>
       <c r="N13" t="n">
         <v>186</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8104</v>
+        <v>2.7017</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.7127</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6551</v>
+        <v>0.625</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8104</v>
+        <v>2.7017</v>
       </c>
       <c r="F14" t="n">
-        <v>2.526</v>
+        <v>1.0709</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2844</v>
+        <v>1.6308</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4401</v>
+        <v>1.0709</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8576</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2844</v>
+        <v>1.6308</v>
       </c>
       <c r="K14" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="M14" t="n">
-        <v>2.142</v>
+        <v>2.2321</v>
       </c>
       <c r="N14" t="n">
-        <v>186</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3499</v>
+        <v>2.3202</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6199</v>
+        <v>0.6121</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4455</v>
+        <v>0.4512</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3499</v>
+        <v>2.3202</v>
       </c>
       <c r="F15" t="n">
-        <v>1.437</v>
+        <v>2.6491</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9129</v>
+        <v>-0.3289</v>
       </c>
       <c r="H15" t="n">
-        <v>1.437</v>
+        <v>3.5032</v>
       </c>
       <c r="I15" t="n">
-        <v>0.776</v>
+        <v>1.967</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9129</v>
+        <v>-0.3289</v>
       </c>
       <c r="K15" t="n">
         <v>132</v>
@@ -1127,7 +1127,7 @@
         <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6889</v>
+        <v>1.6381</v>
       </c>
       <c r="N15" t="n">
         <v>186</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3166</v>
+        <v>2.2395</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6111</v>
+        <v>0.5908</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4304</v>
+        <v>0.4144</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3166</v>
+        <v>2.2395</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3166</v>
+        <v>2.2395</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3453</v>
+        <v>2.2395</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3453</v>
+        <v>2.2395</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3453</v>
+        <v>2.2395</v>
       </c>
       <c r="N16" t="n">
         <v>148</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2419</v>
+        <v>2.2032</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5914</v>
+        <v>0.5812</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3964</v>
+        <v>0.3979</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2419</v>
+        <v>2.2032</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>2.3597</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3581</v>
+        <v>-0.1565</v>
       </c>
       <c r="H17" t="n">
-        <v>3.684</v>
+        <v>2.4166</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9894</v>
+        <v>1.3569</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3581</v>
+        <v>-0.1565</v>
       </c>
       <c r="K17" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6313</v>
+        <v>1.2004</v>
       </c>
       <c r="N17" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1929</v>
+        <v>2.1308</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5785</v>
+        <v>0.5621</v>
       </c>
       <c r="D18" t="n">
-        <v>0.374</v>
+        <v>0.3649</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1929</v>
+        <v>2.1308</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2755</v>
+        <v>1.2904</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.8404</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6136</v>
+        <v>1.2904</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4113</v>
+        <v>0.7245</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.8404</v>
       </c>
       <c r="K18" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3287</v>
+        <v>1.5649</v>
       </c>
       <c r="N18" t="n">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9605</v>
+        <v>1.9083</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5172</v>
+        <v>0.5034</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2683</v>
+        <v>0.2635</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9605</v>
+        <v>1.9083</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1511</v>
+        <v>2.1057</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1906</v>
+        <v>-0.1974</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2031</v>
+        <v>2.1057</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1896</v>
+        <v>1.1823</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1906</v>
+        <v>-0.1974</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>82</v>
       </c>
       <c r="M19" t="n">
-        <v>0.999</v>
+        <v>0.9848999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>200</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.887</v>
+        <v>1.7356</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4978</v>
+        <v>0.4578</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2348</v>
+        <v>0.1849</v>
       </c>
       <c r="E20" t="n">
-        <v>1.887</v>
+        <v>1.7356</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1419</v>
+        <v>2.0079</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2549</v>
+        <v>-0.2723</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1727</v>
+        <v>2.0079</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1732</v>
+        <v>1.1274</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2549</v>
+        <v>-0.2723</v>
       </c>
       <c r="K20" t="n">
         <v>118</v>
@@ -1357,7 +1357,7 @@
         <v>82</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9183</v>
+        <v>0.8551</v>
       </c>
       <c r="N20" t="n">
         <v>200</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4043</v>
+        <v>1.3734</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3704</v>
+        <v>0.3623</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0151</v>
+        <v>0.0199</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4043</v>
+        <v>1.3734</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4043</v>
+        <v>1.3734</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4043</v>
+        <v>1.3734</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4043</v>
+        <v>1.3734</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4043</v>
+        <v>1.3734</v>
       </c>
       <c r="N21" t="n">
         <v>111</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3085</v>
+        <v>1.2799</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3452</v>
+        <v>0.3376</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0285</v>
+        <v>-0.0227</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3085</v>
+        <v>1.2799</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9548</v>
+        <v>1.893</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6463</v>
+        <v>-0.6131</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9548</v>
+        <v>1.893</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0556</v>
+        <v>1.0628</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6463</v>
+        <v>-0.6131</v>
       </c>
       <c r="K22" t="n">
         <v>132</v>
@@ -1449,7 +1449,7 @@
         <v>54</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4093000000000001</v>
+        <v>0.4497</v>
       </c>
       <c r="N22" t="n">
         <v>186</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1961</v>
+        <v>1.1356</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3155</v>
+        <v>0.2996</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0885</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1961</v>
+        <v>1.1356</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1961</v>
+        <v>1.1356</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1961</v>
+        <v>1.1356</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1961</v>
+        <v>1.1356</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1961</v>
+        <v>1.1356</v>
       </c>
       <c r="N23" t="n">
         <v>111</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0486</v>
+        <v>1.0689</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2766</v>
+        <v>0.282</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1469</v>
+        <v>-0.1189</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0486</v>
+        <v>1.0689</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0486</v>
+        <v>1.0689</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0486</v>
+        <v>1.0689</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0486</v>
+        <v>1.0689</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0486</v>
+        <v>1.0689</v>
       </c>
       <c r="N24" t="n">
         <v>111</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9055</v>
+        <v>0.7653</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2389</v>
+        <v>0.2019</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.212</v>
+        <v>-0.2572</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9055</v>
+        <v>0.7653</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9055</v>
+        <v>0.7653</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9055</v>
+        <v>0.7653</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9055</v>
+        <v>0.7653</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9055</v>
+        <v>0.7653</v>
       </c>
       <c r="N25" t="n">
         <v>91</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4049</v>
+        <v>0.3575</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1068</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4399</v>
+        <v>-0.4429</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4049</v>
+        <v>0.3575</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4049</v>
+        <v>0.3575</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4049</v>
+        <v>0.3575</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4049</v>
+        <v>0.3575</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4049</v>
+        <v>0.3575</v>
       </c>
       <c r="N26" t="n">
         <v>111</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2723</v>
+        <v>0.2426</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0718</v>
+        <v>0.064</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5002</v>
+        <v>-0.4953</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2723</v>
+        <v>0.2426</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2723</v>
+        <v>0.2426</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2723</v>
+        <v>0.2426</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2723</v>
+        <v>0.2426</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2723</v>
+        <v>0.2426</v>
       </c>
       <c r="N27" t="n">
         <v>70</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0868</v>
+        <v>0.0543</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0229</v>
+        <v>0.0143</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5847</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0868</v>
+        <v>0.0543</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0868</v>
+        <v>0.0543</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0868</v>
+        <v>0.0543</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0868</v>
+        <v>0.0543</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0868</v>
+        <v>0.0543</v>
       </c>
       <c r="N28" t="n">
         <v>91</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0535</v>
+        <v>-0.0236</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0141</v>
+        <v>-0.0062</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5998</v>
+        <v>-0.6165</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0535</v>
+        <v>-0.0236</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0535</v>
+        <v>-0.0236</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0535</v>
+        <v>-0.0236</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0535</v>
+        <v>-0.0236</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0535</v>
+        <v>-0.0236</v>
       </c>
       <c r="N29" t="n">
         <v>148</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0072</v>
+        <v>-0.0682</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0019</v>
+        <v>-0.018</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.6369</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0072</v>
+        <v>-0.0682</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0072</v>
+        <v>-0.0682</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0072</v>
+        <v>-0.0682</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0072</v>
+        <v>-0.0682</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0072</v>
+        <v>-0.0682</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2627</v>
+        <v>-0.2762</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0693</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7438</v>
+        <v>-0.7316</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2627</v>
+        <v>-0.2762</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2627</v>
+        <v>-0.2762</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2627</v>
+        <v>-0.2762</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2627</v>
+        <v>-0.2762</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2627</v>
+        <v>-0.2762</v>
       </c>
       <c r="N31" t="n">
         <v>148</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2853</v>
+        <v>-0.2845</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7541</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2853</v>
+        <v>-0.2845</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2853</v>
+        <v>-0.2845</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2853</v>
+        <v>-0.2845</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2853</v>
+        <v>-0.2845</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2853</v>
+        <v>-0.2845</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3281</v>
+        <v>-0.3556</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0866</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7736</v>
+        <v>-0.7678</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3281</v>
+        <v>-0.3556</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3281</v>
+        <v>-0.3556</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3281</v>
+        <v>-0.3556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3281</v>
+        <v>-0.3556</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3281</v>
+        <v>-0.3556</v>
       </c>
       <c r="N33" t="n">
         <v>111</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6732</v>
+        <v>-0.4902</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1776</v>
+        <v>-0.1293</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9307</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6732</v>
+        <v>-0.4902</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6732</v>
+        <v>-1.7955</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.3053</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6732</v>
+        <v>-1.7955</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6732</v>
+        <v>-1.0081</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.3053</v>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6732</v>
+        <v>0.2971999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>91</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7413</v>
+        <v>-0.7108</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1956</v>
+        <v>-0.1875</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9617</v>
+        <v>-0.9296</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7413</v>
+        <v>-0.7108</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.0213</v>
+        <v>-0.7108</v>
       </c>
       <c r="G35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-2.0213</v>
+        <v>-0.7108</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0915</v>
+        <v>-0.7108</v>
       </c>
       <c r="J35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="L35" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1885000000000001</v>
+        <v>-0.7108</v>
       </c>
       <c r="N35" t="n">
-        <v>342</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7548</v>
+        <v>-0.7155</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1991</v>
+        <v>-0.1887</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9678</v>
+        <v>-0.9317</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7548</v>
+        <v>-0.7155</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7548</v>
+        <v>-0.7155</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7548</v>
+        <v>-0.7155</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7548</v>
+        <v>-0.7155</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7548</v>
+        <v>-0.7155</v>
       </c>
       <c r="N36" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9873</v>
+        <v>-0.9438</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2604</v>
+        <v>-0.249</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0736</v>
+        <v>-1.0357</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9873</v>
+        <v>-0.9438</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9873</v>
+        <v>-0.9438</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9873</v>
+        <v>-0.9438</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9873</v>
+        <v>-0.9438</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9873</v>
+        <v>-0.9438</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1633</v>
+        <v>-1.1234</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3069</v>
+        <v>-0.2963</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1538</v>
+        <v>-1.1176</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1633</v>
+        <v>-1.1234</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1633</v>
+        <v>-1.1234</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1633</v>
+        <v>-1.1234</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1633</v>
+        <v>-1.1234</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1633</v>
+        <v>-1.1234</v>
       </c>
       <c r="N38" t="n">
         <v>148</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.184</v>
+        <v>-1.1454</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3123</v>
+        <v>-0.3022</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1632</v>
+        <v>-1.1276</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.184</v>
+        <v>-1.1454</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.184</v>
+        <v>-1.1454</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.184</v>
+        <v>-1.1454</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.184</v>
+        <v>-1.1454</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.184</v>
+        <v>-1.1454</v>
       </c>
       <c r="N39" t="n">
         <v>91</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2817</v>
+        <v>-1.263</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3381</v>
+        <v>-0.3332</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2077</v>
+        <v>-1.1811</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2817</v>
+        <v>-1.263</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2817</v>
+        <v>-1.263</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2817</v>
+        <v>-1.263</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2817</v>
+        <v>-1.263</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2817</v>
+        <v>-1.263</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2096</v>
+        <v>-2.2769</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5829</v>
+        <v>-0.6006</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6301</v>
+        <v>-1.643</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2096</v>
+        <v>-2.2769</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4737</v>
+        <v>-0.5429</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.7359</v>
+        <v>-1.734</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4737</v>
+        <v>-0.5429</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2558</v>
+        <v>-0.3048</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.7359</v>
+        <v>-1.734</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>173</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9917</v>
+        <v>-2.0388</v>
       </c>
       <c r="N41" t="n">
         <v>278</v>
@@ -2429,10 +2429,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3082</v>
+        <v>1.3385</v>
       </c>
       <c r="J2" t="n">
-        <v>31.3968</v>
+        <v>32.124</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1513</v>
+        <v>1.1637</v>
       </c>
       <c r="J3" t="n">
-        <v>27.6312</v>
+        <v>27.9288</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8821</v>
+        <v>0.8716</v>
       </c>
       <c r="J4" t="n">
-        <v>21.1704</v>
+        <v>20.9184</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7691</v>
+        <v>0.7517</v>
       </c>
       <c r="J5" t="n">
-        <v>18.4584</v>
+        <v>18.0408</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.17</v>
+        <v>0.1412</v>
       </c>
       <c r="J6" t="n">
-        <v>4.08</v>
+        <v>3.3888</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.17</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4558</v>
+        <v>0.41</v>
       </c>
       <c r="J7" t="n">
-        <v>10.9392</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.86</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1712</v>
+        <v>-0.1553</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.1088</v>
+        <v>-3.7272</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2791</v>
+        <v>-0.2622</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.6984</v>
+        <v>-6.2928</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.57</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.442</v>
+        <v>-0.4342</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.608</v>
+        <v>-10.4208</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4683</v>
+        <v>-0.4634</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.2392</v>
+        <v>-11.1216</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2108</v>
+        <v>-0.1954</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.4268</v>
+        <v>-4.1034</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2624</v>
+        <v>-0.249</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.5104</v>
+        <v>-5.229</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4246</v>
+        <v>-0.4163</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.916600000000001</v>
+        <v>-8.7423</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4422</v>
+        <v>-0.4351</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.286199999999999</v>
+        <v>-9.1371</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.54</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.451</v>
+        <v>-0.4445</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.471</v>
+        <v>-9.3345</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9285</v>
+        <v>0.8598</v>
       </c>
       <c r="J17" t="n">
-        <v>19.4985</v>
+        <v>18.0558</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.76</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8389</v>
+        <v>0.7683</v>
       </c>
       <c r="J18" t="n">
-        <v>17.6169</v>
+        <v>16.1343</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.43</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5301</v>
+        <v>0.4659</v>
       </c>
       <c r="J19" t="n">
-        <v>11.1321</v>
+        <v>9.783899999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2799</v>
+        <v>0.2324</v>
       </c>
       <c r="J20" t="n">
-        <v>5.8779</v>
+        <v>4.8804</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0315</v>
+        <v>-0.0306</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6615</v>
+        <v>-0.6425999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9683</v>
+        <v>0.9567</v>
       </c>
       <c r="J22" t="n">
-        <v>24.2075</v>
+        <v>23.9175</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.441</v>
+        <v>0.403</v>
       </c>
       <c r="J23" t="n">
-        <v>11.025</v>
+        <v>10.075</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.13</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3945</v>
+        <v>0.3571</v>
       </c>
       <c r="J24" t="n">
-        <v>9.862500000000001</v>
+        <v>8.9275</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J25" t="n">
-        <v>9.262499999999999</v>
+        <v>8.342499999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4458</v>
+        <v>-0.4038</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.145</v>
+        <v>-10.095</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.02</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0604</v>
       </c>
       <c r="J27" t="n">
-        <v>2.115</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0604</v>
       </c>
       <c r="J28" t="n">
-        <v>2.115</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0538</v>
+        <v>0.0364</v>
       </c>
       <c r="J29" t="n">
-        <v>1.345</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2457</v>
+        <v>-0.2258</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.1425</v>
+        <v>-5.645</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2555</v>
+        <v>-0.2358</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.3875</v>
+        <v>-5.895</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.45</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6393</v>
+        <v>0.672</v>
       </c>
       <c r="J32" t="n">
-        <v>18.5397</v>
+        <v>19.488</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1469</v>
+        <v>0.1308</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2601</v>
+        <v>3.7932</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0602</v>
+        <v>-0.0471</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.7458</v>
+        <v>-1.3659</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1138</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.3002</v>
+        <v>-2.7753</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3316</v>
+        <v>-0.3159</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.616400000000001</v>
+        <v>-9.161099999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5599</v>
+        <v>0.4896</v>
       </c>
       <c r="J37" t="n">
-        <v>16.2371</v>
+        <v>14.1984</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2533</v>
+        <v>0.205</v>
       </c>
       <c r="J38" t="n">
-        <v>7.3457</v>
+        <v>5.945</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.241</v>
+        <v>0.1941</v>
       </c>
       <c r="J39" t="n">
-        <v>6.989</v>
+        <v>5.6289</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2283</v>
+        <v>0.1831</v>
       </c>
       <c r="J40" t="n">
-        <v>6.6207</v>
+        <v>5.3099</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1711</v>
+        <v>-0.1511</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.9619</v>
+        <v>-4.3819</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.38</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J42" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0172</v>
+        <v>1.0214</v>
       </c>
       <c r="J43" t="n">
-        <v>20.344</v>
+        <v>20.428</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8724</v>
+        <v>0.8653</v>
       </c>
       <c r="J44" t="n">
-        <v>17.448</v>
+        <v>17.306</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3683</v>
+        <v>0.3356</v>
       </c>
       <c r="J45" t="n">
-        <v>7.366</v>
+        <v>6.712</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.526</v>
+        <v>-1.516</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2015</v>
+        <v>-0.1858</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.03</v>
+        <v>-3.716</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2121</v>
+        <v>-0.1969</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.242</v>
+        <v>-3.938</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.64</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3646</v>
+        <v>-0.3538</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.292</v>
+        <v>-7.076</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.59</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4079</v>
+        <v>-0.3985</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.157999999999999</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.4</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5748</v>
+        <v>-0.5828</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.496</v>
+        <v>-11.656</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.03</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1262</v>
+        <v>0.0958</v>
       </c>
       <c r="J52" t="n">
-        <v>3.155</v>
+        <v>2.395</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.159</v>
+        <v>-0.1415</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.975</v>
+        <v>-3.5375</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1695</v>
+        <v>-0.1515</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.2375</v>
+        <v>-3.7875</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2099</v>
+        <v>-0.1909</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.2475</v>
+        <v>-4.7725</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3161</v>
+        <v>-0.299</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.9025</v>
+        <v>-7.475</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0531</v>
+        <v>1.0594</v>
       </c>
       <c r="J57" t="n">
-        <v>26.3275</v>
+        <v>26.485</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6041</v>
+        <v>0.5735</v>
       </c>
       <c r="J58" t="n">
-        <v>15.1025</v>
+        <v>14.3375</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5831</v>
+        <v>0.5521</v>
       </c>
       <c r="J59" t="n">
-        <v>14.5775</v>
+        <v>13.8025</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.17</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4732</v>
+        <v>0.4404</v>
       </c>
       <c r="J60" t="n">
-        <v>11.83</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.14</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4029</v>
+        <v>0.3699</v>
       </c>
       <c r="J61" t="n">
-        <v>10.0725</v>
+        <v>9.2475</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.67</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7813</v>
+        <v>0.7097</v>
       </c>
       <c r="J62" t="n">
-        <v>17.9699</v>
+        <v>16.3231</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5129</v>
+        <v>0.4454</v>
       </c>
       <c r="J63" t="n">
-        <v>11.7967</v>
+        <v>10.2442</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.35</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4605</v>
+        <v>0.3959</v>
       </c>
       <c r="J64" t="n">
-        <v>10.5915</v>
+        <v>9.105700000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0453</v>
+        <v>-0.0361</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.0419</v>
+        <v>-0.8303</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1202</v>
+        <v>-0.103</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.7646</v>
+        <v>-2.369</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.15</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2964</v>
+        <v>0.2862</v>
       </c>
       <c r="J67" t="n">
-        <v>6.8172</v>
+        <v>6.5826</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.149</v>
+        <v>-0.1316</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.427</v>
+        <v>-3.0268</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.5384</v>
+        <v>-5.0922</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2604</v>
+        <v>-0.2412</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9892</v>
+        <v>-5.5476</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.27</v>
+        <v>-0.2511</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.21</v>
+        <v>-5.7753</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.04</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1774</v>
+        <v>0.1447</v>
       </c>
       <c r="J72" t="n">
-        <v>3.9028</v>
+        <v>3.1834</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1153</v>
+        <v>-0.1007</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.5366</v>
+        <v>-2.2154</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2334</v>
+        <v>-0.2165</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.1348</v>
+        <v>-4.763</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.326</v>
+        <v>-0.3101</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.172</v>
+        <v>-6.8222</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.48</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5214</v>
+        <v>-0.5232</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.4708</v>
+        <v>-11.5104</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5207</v>
+        <v>1.5542</v>
       </c>
       <c r="J77" t="n">
-        <v>33.4554</v>
+        <v>34.1924</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.35</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8139</v>
       </c>
       <c r="J78" t="n">
-        <v>18.2402</v>
+        <v>17.9058</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.35</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8139</v>
       </c>
       <c r="J79" t="n">
-        <v>18.2402</v>
+        <v>17.9058</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8104</v>
+        <v>0.7941</v>
       </c>
       <c r="J80" t="n">
-        <v>17.8288</v>
+        <v>17.4702</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4316</v>
+        <v>-0.3951</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.495200000000001</v>
+        <v>-8.6922</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7024</v>
+        <v>0.6718</v>
       </c>
       <c r="J82" t="n">
-        <v>19.6672</v>
+        <v>18.8104</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.5708</v>
+        <v>-1.2488</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1979</v>
+        <v>-0.1774</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.5412</v>
+        <v>-4.9672</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1979</v>
+        <v>-0.1774</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.5412</v>
+        <v>-4.9672</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3348</v>
+        <v>-0.3188</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.3744</v>
+        <v>-8.926399999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.45</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8796</v>
       </c>
       <c r="J87" t="n">
-        <v>25.0516</v>
+        <v>24.6288</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.26</v>
       </c>
       <c r="I88" t="n">
-        <v>0.615</v>
+        <v>0.6034</v>
       </c>
       <c r="J88" t="n">
-        <v>17.22</v>
+        <v>16.8952</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.14</v>
       </c>
       <c r="I89" t="n">
-        <v>0.414</v>
+        <v>0.3786</v>
       </c>
       <c r="J89" t="n">
-        <v>11.592</v>
+        <v>10.6008</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.4472</v>
+        <v>-1.8592</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.4472</v>
+        <v>-1.8592</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.25</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4944</v>
+        <v>0.4548</v>
       </c>
       <c r="J92" t="n">
-        <v>12.8544</v>
+        <v>11.8248</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4823</v>
+        <v>0.4386</v>
       </c>
       <c r="J93" t="n">
-        <v>12.5398</v>
+        <v>11.4036</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2105</v>
+        <v>0.1686</v>
       </c>
       <c r="J94" t="n">
-        <v>5.473</v>
+        <v>4.3836</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.302</v>
+        <v>-0.2843</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.852</v>
+        <v>-7.3918</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.74</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3115</v>
+        <v>-0.2943</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.099</v>
+        <v>-7.6518</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7136</v>
+        <v>0.698</v>
       </c>
       <c r="J97" t="n">
-        <v>18.5536</v>
+        <v>18.148</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.13</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4058</v>
+        <v>0.3647</v>
       </c>
       <c r="J98" t="n">
-        <v>10.5508</v>
+        <v>9.482200000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3812</v>
+        <v>0.3402</v>
       </c>
       <c r="J99" t="n">
-        <v>9.911199999999999</v>
+        <v>8.8452</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3559</v>
+        <v>0.3155</v>
       </c>
       <c r="J100" t="n">
-        <v>9.253399999999999</v>
+        <v>8.202999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.61</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.0073</v>
+        <v>-1.0059</v>
       </c>
       <c r="J101" t="n">
-        <v>-26.1898</v>
+        <v>-26.1534</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.43</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5313</v>
+        <v>0.4922</v>
       </c>
       <c r="J102" t="n">
-        <v>15.939</v>
+        <v>14.766</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.26</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3757</v>
+        <v>0.3145</v>
       </c>
       <c r="J103" t="n">
-        <v>11.271</v>
+        <v>9.435</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2294</v>
+        <v>0.1835</v>
       </c>
       <c r="J104" t="n">
-        <v>6.882</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0742</v>
       </c>
       <c r="J105" t="n">
-        <v>2.985</v>
+        <v>2.226</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2927</v>
+        <v>-0.2754</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.781000000000001</v>
+        <v>-8.262</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4718</v>
+        <v>0.4894</v>
       </c>
       <c r="J107" t="n">
-        <v>14.154</v>
+        <v>14.682</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.453</v>
+        <v>0.4629</v>
       </c>
       <c r="J108" t="n">
-        <v>13.59</v>
+        <v>13.887</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1119</v>
+        <v>0.0975</v>
       </c>
       <c r="J109" t="n">
-        <v>3.357</v>
+        <v>2.925</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0547</v>
+        <v>0.0447</v>
       </c>
       <c r="J110" t="n">
-        <v>1.641</v>
+        <v>1.341</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.52</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.509</v>
+        <v>-0.5125</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.27</v>
+        <v>-15.375</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3051</v>
+        <v>0.2561</v>
       </c>
       <c r="J112" t="n">
-        <v>6.7122</v>
+        <v>5.6342</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1518</v>
+        <v>0.1176</v>
       </c>
       <c r="J113" t="n">
-        <v>3.3396</v>
+        <v>2.5872</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.85</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1898</v>
+        <v>-0.1711</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.1756</v>
+        <v>-3.7642</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2784</v>
+        <v>-0.2598</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.1248</v>
+        <v>-5.7156</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.57</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4514</v>
+        <v>-0.4453</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.9308</v>
+        <v>-9.7966</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.76</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2669</v>
+        <v>1.2672</v>
       </c>
       <c r="J117" t="n">
-        <v>27.8718</v>
+        <v>27.8784</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7698</v>
+        <v>0.7583</v>
       </c>
       <c r="J118" t="n">
-        <v>16.9356</v>
+        <v>16.6826</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5203</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>11.4466</v>
+        <v>11.3432</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4532</v>
+        <v>0.4286</v>
       </c>
       <c r="J120" t="n">
-        <v>9.9704</v>
+        <v>9.4292</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.16</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4338</v>
+        <v>0.405</v>
       </c>
       <c r="J121" t="n">
-        <v>9.5436</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4892</v>
+        <v>0.4484</v>
       </c>
       <c r="J122" t="n">
-        <v>14.676</v>
+        <v>13.452</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4643</v>
+        <v>0.4154</v>
       </c>
       <c r="J123" t="n">
-        <v>13.929</v>
+        <v>12.462</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1741</v>
+        <v>0.1359</v>
       </c>
       <c r="J124" t="n">
-        <v>5.223</v>
+        <v>4.077</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2302</v>
+        <v>-0.2098</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.906</v>
+        <v>-6.294</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4872</v>
+        <v>-0.4868</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.616</v>
+        <v>-14.604</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.69</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2275</v>
+        <v>1.2296</v>
       </c>
       <c r="J127" t="n">
-        <v>36.825</v>
+        <v>36.888</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.587</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>17.61</v>
+        <v>17.283</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5551</v>
+        <v>0.5457</v>
       </c>
       <c r="J129" t="n">
-        <v>16.653</v>
+        <v>16.371</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.87</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4477</v>
+        <v>-0.4058</v>
       </c>
       <c r="J130" t="n">
-        <v>-13.431</v>
+        <v>-12.174</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8359</v>
+        <v>-0.8174</v>
       </c>
       <c r="J131" t="n">
-        <v>-25.077</v>
+        <v>-24.522</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.67</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2843</v>
+        <v>1.3039</v>
       </c>
       <c r="J132" t="n">
-        <v>25.686</v>
+        <v>26.078</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0939</v>
+        <v>1.109</v>
       </c>
       <c r="J133" t="n">
-        <v>21.878</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.45</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="J134" t="n">
-        <v>19.93</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.37</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8585</v>
+        <v>0.8489</v>
       </c>
       <c r="J135" t="n">
-        <v>17.17</v>
+        <v>16.978</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.15</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3981</v>
+        <v>0.3663</v>
       </c>
       <c r="J136" t="n">
-        <v>7.962</v>
+        <v>7.326</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0876</v>
+        <v>-0.0659</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.752</v>
+        <v>-1.318</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.68</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3253</v>
+        <v>-0.3148</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.506</v>
+        <v>-6.296</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4473</v>
+        <v>-0.441</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.946</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.5</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4825</v>
+        <v>-0.4789</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.65</v>
+        <v>-9.577999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5177</v>
+        <v>-0.5178</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.354</v>
+        <v>-10.356</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2834</v>
+        <v>1.3087</v>
       </c>
       <c r="J142" t="n">
-        <v>37.2186</v>
+        <v>37.9523</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1618</v>
+        <v>0.1335</v>
       </c>
       <c r="J143" t="n">
-        <v>4.6922</v>
+        <v>3.8715</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="J144" t="n">
-        <v>2.6912</v>
+        <v>2.117</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0076</v>
+        <v>-0.0046</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.2204</v>
+        <v>-0.1334</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.007</v>
+        <v>-1.0055</v>
       </c>
       <c r="J146" t="n">
-        <v>-29.203</v>
+        <v>-29.1595</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>0.822</v>
+        <v>0.7693</v>
       </c>
       <c r="J147" t="n">
-        <v>23.838</v>
+        <v>22.3097</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.09</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2244</v>
+        <v>0.1822</v>
       </c>
       <c r="J148" t="n">
-        <v>6.5076</v>
+        <v>5.2838</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.142</v>
+        <v>0.1107</v>
       </c>
       <c r="J149" t="n">
-        <v>4.118</v>
+        <v>3.2103</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.84</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2169</v>
+        <v>-0.1964</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.2901</v>
+        <v>-5.6956</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.84</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2169</v>
+        <v>-0.1964</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.2901</v>
+        <v>-5.6956</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.18</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3823</v>
+        <v>0.328</v>
       </c>
       <c r="J152" t="n">
-        <v>11.469</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.348</v>
+        <v>0.2959</v>
       </c>
       <c r="J153" t="n">
-        <v>10.44</v>
+        <v>8.877000000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2019</v>
+        <v>0.1635</v>
       </c>
       <c r="J154" t="n">
-        <v>6.057</v>
+        <v>4.905</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1607</v>
+        <v>0.1277</v>
       </c>
       <c r="J155" t="n">
-        <v>4.821</v>
+        <v>3.831</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0511</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.953</v>
+        <v>-1.533</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.53</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1671</v>
+        <v>1.1823</v>
       </c>
       <c r="J157" t="n">
-        <v>35.013</v>
+        <v>35.469</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3963</v>
+        <v>0.3579</v>
       </c>
       <c r="J158" t="n">
-        <v>11.889</v>
+        <v>10.737</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3722</v>
+        <v>0.3344</v>
       </c>
       <c r="J159" t="n">
-        <v>11.166</v>
+        <v>10.032</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1526</v>
+        <v>0.1272</v>
       </c>
       <c r="J160" t="n">
-        <v>4.578</v>
+        <v>3.816</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7227</v>
+        <v>-0.6933</v>
       </c>
       <c r="J161" t="n">
-        <v>-21.681</v>
+        <v>-20.799</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.05</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1617</v>
+        <v>0.1249</v>
       </c>
       <c r="J162" t="n">
-        <v>4.851</v>
+        <v>3.747</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.02</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0853</v>
+        <v>0.0611</v>
       </c>
       <c r="J163" t="n">
-        <v>2.559</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.86</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1841</v>
+        <v>-0.1643</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.523</v>
+        <v>-4.929</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.86</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1841</v>
+        <v>-0.1643</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.523</v>
+        <v>-4.929</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2152</v>
+        <v>-0.195</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.456</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.57</v>
       </c>
       <c r="I167" t="n">
-        <v>1.181</v>
+        <v>1.1952</v>
       </c>
       <c r="J167" t="n">
-        <v>35.43</v>
+        <v>35.856</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.32</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7789</v>
+        <v>0.7572</v>
       </c>
       <c r="J168" t="n">
-        <v>23.367</v>
+        <v>22.716</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.74</v>
+        <v>0.7165</v>
       </c>
       <c r="J169" t="n">
-        <v>22.2</v>
+        <v>21.495</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.27</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6815</v>
+        <v>0.6554</v>
       </c>
       <c r="J170" t="n">
-        <v>20.445</v>
+        <v>19.662</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1862</v>
+        <v>-0.1561</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.586</v>
+        <v>-4.683</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.23</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4115</v>
+        <v>0.4147</v>
       </c>
       <c r="J172" t="n">
-        <v>9.875999999999999</v>
+        <v>9.9528</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.254</v>
+        <v>0.241</v>
       </c>
       <c r="J173" t="n">
-        <v>6.096</v>
+        <v>5.784</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0523</v>
+        <v>0.042</v>
       </c>
       <c r="J174" t="n">
-        <v>1.2552</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5036</v>
+        <v>-0.5041</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.0864</v>
+        <v>-12.0984</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.47</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5431</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.9072</v>
+        <v>-13.0344</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.62</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7238</v>
+        <v>0.6518</v>
       </c>
       <c r="J177" t="n">
-        <v>17.3712</v>
+        <v>15.6432</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5273</v>
+        <v>0.4603</v>
       </c>
       <c r="J178" t="n">
-        <v>12.6552</v>
+        <v>11.0472</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.39</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4967</v>
+        <v>0.4315</v>
       </c>
       <c r="J179" t="n">
-        <v>11.9208</v>
+        <v>10.356</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.25</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3482</v>
+        <v>0.2939</v>
       </c>
       <c r="J180" t="n">
-        <v>8.3568</v>
+        <v>7.0536</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0497</v>
+        <v>-0.041</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.1928</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3612</v>
+        <v>1.3838</v>
       </c>
       <c r="J182" t="n">
-        <v>31.3076</v>
+        <v>31.8274</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.68</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3108</v>
+        <v>1.3307</v>
       </c>
       <c r="J183" t="n">
-        <v>30.1484</v>
+        <v>30.6061</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.17</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4573</v>
+        <v>0.4266</v>
       </c>
       <c r="J184" t="n">
-        <v>10.5179</v>
+        <v>9.8118</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3373</v>
+        <v>0.3053</v>
       </c>
       <c r="J185" t="n">
-        <v>7.7579</v>
+        <v>7.0219</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.175</v>
+        <v>0.1466</v>
       </c>
       <c r="J186" t="n">
-        <v>4.025</v>
+        <v>3.3718</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2322</v>
+        <v>0.1954</v>
       </c>
       <c r="J187" t="n">
-        <v>5.3406</v>
+        <v>4.4942</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0061</v>
+        <v>0.0146</v>
       </c>
       <c r="J188" t="n">
-        <v>0.1403</v>
+        <v>0.3358</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.64</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3787</v>
+        <v>-0.3657</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.710100000000001</v>
+        <v>-8.411099999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.63</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3877</v>
+        <v>-0.3753</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.9171</v>
+        <v>-8.6319</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4762</v>
+        <v>-0.4721</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.9526</v>
+        <v>-10.8583</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.64</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2891</v>
+        <v>1.3086</v>
       </c>
       <c r="J192" t="n">
-        <v>28.3602</v>
+        <v>28.7892</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.32</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7904</v>
+        <v>0.766</v>
       </c>
       <c r="J193" t="n">
-        <v>17.3888</v>
+        <v>16.852</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6068</v>
+        <v>0.5747</v>
       </c>
       <c r="J194" t="n">
-        <v>13.3496</v>
+        <v>12.6434</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.16</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4549</v>
+        <v>0.4208</v>
       </c>
       <c r="J195" t="n">
-        <v>10.0078</v>
+        <v>9.2576</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8046</v>
+        <v>-0.7851</v>
       </c>
       <c r="J196" t="n">
-        <v>-17.7012</v>
+        <v>-17.2722</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3175</v>
+        <v>0.2669</v>
       </c>
       <c r="J197" t="n">
-        <v>6.985</v>
+        <v>5.8718</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.0086</v>
+        <v>-1.7028</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2019</v>
+        <v>-0.1824</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.4418</v>
+        <v>-4.0128</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2518</v>
+        <v>-0.2324</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.5396</v>
+        <v>-5.1128</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2808</v>
+        <v>-0.2621</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.1776</v>
+        <v>-5.7662</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4139</v>
+        <v>0.3672</v>
       </c>
       <c r="J202" t="n">
-        <v>9.5197</v>
+        <v>8.445600000000001</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.9</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1272</v>
+        <v>-0.1122</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.9256</v>
+        <v>-2.5806</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2705</v>
+        <v>-0.2534</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.2215</v>
+        <v>-5.8282</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3625</v>
+        <v>-0.3483</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.3375</v>
+        <v>-8.010899999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.46</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5386</v>
+        <v>-0.5429</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.3878</v>
+        <v>-12.4867</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.83</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4906</v>
+        <v>1.5215</v>
       </c>
       <c r="J207" t="n">
-        <v>34.2838</v>
+        <v>34.9945</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.113</v>
+        <v>1.1272</v>
       </c>
       <c r="J208" t="n">
-        <v>25.599</v>
+        <v>25.9256</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6692</v>
+        <v>0.6466</v>
       </c>
       <c r="J209" t="n">
-        <v>15.3916</v>
+        <v>14.8718</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.15</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4056</v>
+        <v>0.3741</v>
       </c>
       <c r="J210" t="n">
-        <v>9.328799999999999</v>
+        <v>8.6043</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.13</v>
       </c>
       <c r="I211" t="n">
-        <v>0.3572</v>
+        <v>0.3251</v>
       </c>
       <c r="J211" t="n">
-        <v>8.2156</v>
+        <v>7.4773</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1377</v>
+        <v>0.1074</v>
       </c>
       <c r="J212" t="n">
-        <v>3.3048</v>
+        <v>2.5776</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0068</v>
+        <v>-0.0025</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.1632</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0965</v>
+        <v>-0.0828</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.316</v>
+        <v>-1.9872</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4119</v>
+        <v>-0.4015</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.8856</v>
+        <v>-9.635999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.57</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4473</v>
+        <v>-0.4404</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.7352</v>
+        <v>-10.5696</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3482</v>
+        <v>1.3702</v>
       </c>
       <c r="J217" t="n">
-        <v>32.3568</v>
+        <v>32.8848</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.68</v>
       </c>
       <c r="I218" t="n">
-        <v>1.3227</v>
+        <v>1.3432</v>
       </c>
       <c r="J218" t="n">
-        <v>31.7448</v>
+        <v>32.2368</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.18</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4891</v>
+        <v>0.4579</v>
       </c>
       <c r="J219" t="n">
-        <v>11.7384</v>
+        <v>10.9896</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.221</v>
+        <v>-0.1882</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.304</v>
+        <v>-4.5168</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2833</v>
+        <v>-0.247</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.7992</v>
+        <v>-5.928</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.09</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2551</v>
+        <v>0.2087</v>
       </c>
       <c r="J222" t="n">
-        <v>7.1428</v>
+        <v>5.8436</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="J223" t="n">
-        <v>2.5424</v>
+        <v>1.8424</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.84</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2026</v>
+        <v>-0.1829</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.6728</v>
+        <v>-5.1212</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.79</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2526</v>
+        <v>-0.2331</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.0728</v>
+        <v>-6.5268</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2912</v>
+        <v>-0.2727</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.153600000000001</v>
+        <v>-7.6356</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.61</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2554</v>
+        <v>1.2735</v>
       </c>
       <c r="J227" t="n">
-        <v>35.1512</v>
+        <v>35.658</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6728</v>
+        <v>0.6415</v>
       </c>
       <c r="J228" t="n">
-        <v>18.8384</v>
+        <v>17.962</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3118</v>
+        <v>0.2788</v>
       </c>
       <c r="J229" t="n">
-        <v>8.730399999999999</v>
+        <v>7.8064</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2303</v>
+        <v>0.2005</v>
       </c>
       <c r="J230" t="n">
-        <v>6.4484</v>
+        <v>5.614</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3514</v>
+        <v>-0.3104</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.8392</v>
+        <v>-8.6912</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.36</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8762</v>
+        <v>0.8568</v>
       </c>
       <c r="J232" t="n">
-        <v>29.7908</v>
+        <v>29.1312</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.22</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5896</v>
+        <v>0.5554</v>
       </c>
       <c r="J233" t="n">
-        <v>20.0464</v>
+        <v>18.8836</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4358</v>
+        <v>0.4004</v>
       </c>
       <c r="J234" t="n">
-        <v>14.8172</v>
+        <v>13.6136</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.14</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4122</v>
+        <v>0.3771</v>
       </c>
       <c r="J235" t="n">
-        <v>14.0148</v>
+        <v>12.8214</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1722</v>
+        <v>0.1459</v>
       </c>
       <c r="J236" t="n">
-        <v>5.8548</v>
+        <v>4.9606</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.2</v>
       </c>
       <c r="I237" t="n">
-        <v>0.45</v>
+        <v>0.393</v>
       </c>
       <c r="J237" t="n">
-        <v>15.3</v>
+        <v>13.362</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0078</v>
+        <v>0.0047</v>
       </c>
       <c r="J238" t="n">
-        <v>0.2652</v>
+        <v>0.1598</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.86</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1853</v>
+        <v>-0.1653</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.3002</v>
+        <v>-5.6202</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2062</v>
+        <v>-0.186</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.0108</v>
+        <v>-6.324</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2565</v>
+        <v>-0.2368</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.721</v>
+        <v>-8.0512</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.7</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3345</v>
+        <v>1.3556</v>
       </c>
       <c r="J242" t="n">
-        <v>30.6935</v>
+        <v>31.1788</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.69</v>
       </c>
       <c r="I243" t="n">
-        <v>1.322</v>
+        <v>1.3424</v>
       </c>
       <c r="J243" t="n">
-        <v>30.406</v>
+        <v>30.8752</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.43</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9725</v>
+        <v>0.9701</v>
       </c>
       <c r="J244" t="n">
-        <v>22.3675</v>
+        <v>22.3123</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4093</v>
+        <v>0.3778</v>
       </c>
       <c r="J245" t="n">
-        <v>9.4139</v>
+        <v>8.689399999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6034</v>
+        <v>-0.5728</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.8782</v>
+        <v>-13.1744</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.89</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1348</v>
+        <v>-0.1196</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.1004</v>
+        <v>-2.7508</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.73</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2958</v>
+        <v>-0.2797</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.8034</v>
+        <v>-6.4331</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2958</v>
+        <v>-0.2797</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.8034</v>
+        <v>-6.4331</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.73</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2958</v>
+        <v>-0.2797</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.8034</v>
+        <v>-6.4331</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.72</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3049</v>
+        <v>-0.2889</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.0127</v>
+        <v>-6.6447</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.18</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4429</v>
+        <v>0.3901</v>
       </c>
       <c r="J252" t="n">
-        <v>11.5154</v>
+        <v>10.1426</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1989</v>
+        <v>-0.1804</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.1714</v>
+        <v>-4.6904</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1989</v>
+        <v>-0.1804</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.1714</v>
+        <v>-4.6904</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2286</v>
+        <v>-0.2097</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.9436</v>
+        <v>-5.4522</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.59</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4324</v>
+        <v>-0.4241</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.2424</v>
+        <v>-11.0266</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.43</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9866</v>
+        <v>0.9829</v>
       </c>
       <c r="J257" t="n">
-        <v>25.6516</v>
+        <v>25.5554</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9522</v>
+        <v>0.9432</v>
       </c>
       <c r="J258" t="n">
-        <v>24.7572</v>
+        <v>24.5232</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.32</v>
       </c>
       <c r="I259" t="n">
-        <v>0.781</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>20.306</v>
+        <v>19.7236</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.15</v>
       </c>
       <c r="I260" t="n">
-        <v>0.423</v>
+        <v>0.3906</v>
       </c>
       <c r="J260" t="n">
-        <v>10.998</v>
+        <v>10.1556</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.1259</v>
+        <v>0.1023</v>
       </c>
       <c r="J261" t="n">
-        <v>3.2734</v>
+        <v>2.6598</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.55</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1401</v>
+        <v>1.1546</v>
       </c>
       <c r="J262" t="n">
-        <v>25.0822</v>
+        <v>25.4012</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.49</v>
       </c>
       <c r="I263" t="n">
-        <v>1.061</v>
+        <v>1.0714</v>
       </c>
       <c r="J263" t="n">
-        <v>23.342</v>
+        <v>23.5708</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.43</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9705</v>
+        <v>0.9685</v>
       </c>
       <c r="J264" t="n">
-        <v>21.351</v>
+        <v>21.307</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.22</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5652</v>
+        <v>0.538</v>
       </c>
       <c r="J265" t="n">
-        <v>12.4344</v>
+        <v>11.836</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.18</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4766</v>
+        <v>0.4465</v>
       </c>
       <c r="J266" t="n">
-        <v>10.4852</v>
+        <v>9.823</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.05</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2519</v>
+        <v>0.2272</v>
       </c>
       <c r="J267" t="n">
-        <v>5.5418</v>
+        <v>4.9984</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.71</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3068</v>
+        <v>-0.2938</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.7496</v>
+        <v>-6.4636</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3247</v>
+        <v>-0.3119</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.1434</v>
+        <v>-6.8618</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.54</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4562</v>
+        <v>-0.4499</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.0364</v>
+        <v>-9.8978</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.41</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.57</v>
+        <v>-0.5777</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.54</v>
+        <v>-12.7094</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.37</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9061</v>
+        <v>0.8887</v>
       </c>
       <c r="J272" t="n">
-        <v>27.183</v>
+        <v>26.661</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.31</v>
       </c>
       <c r="I273" t="n">
-        <v>0.7855</v>
+        <v>0.7585</v>
       </c>
       <c r="J273" t="n">
-        <v>23.565</v>
+        <v>22.755</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4399</v>
+        <v>0.4025</v>
       </c>
       <c r="J274" t="n">
-        <v>13.197</v>
+        <v>12.075</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.99</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0834</v>
+        <v>-0.0626</v>
       </c>
       <c r="J275" t="n">
-        <v>-2.502</v>
+        <v>-1.878</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.37</v>
+        <v>-0.328</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.1</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.55</v>
       </c>
       <c r="I277" t="n">
-        <v>0.9704</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>29.112</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3658</v>
+        <v>0.3111</v>
       </c>
       <c r="J278" t="n">
-        <v>10.974</v>
+        <v>9.333</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.281</v>
+        <v>-0.2622</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.43</v>
+        <v>-7.866</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.77</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.281</v>
+        <v>-0.2622</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.43</v>
+        <v>-7.866</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.71</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3377</v>
+        <v>-0.3221</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.131</v>
+        <v>-9.663</v>
       </c>
     </row>
   </sheetData>
